--- a/erp-server/erp-server-file/src/main/resources/excel/mrp/salesCalc.xlsx
+++ b/erp-server/erp-server-file/src/main/resources/excel/mrp/salesCalc.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="12255"/>
+    <workbookView windowWidth="28800" windowHeight="12255" activeTab="3"/>
   </bookViews>
   <sheets>
     <sheet name="1 - 历史销量 &amp; 去噪销量" sheetId="2" r:id="rId1"/>
@@ -267,31 +267,31 @@
     <t>{.fixedValue}</t>
   </si>
   <si>
-    <t>{.percentJsonDTO.threeDaysRatio}</t>
+    <t>{.threeDaysRatio}</t>
   </si>
   <si>
-    <t>{.percentJsonDTO.sevenDaysRatio}</t>
+    <t>{.sevenDaysRatio}</t>
   </si>
   <si>
-    <t>{.percentJsonDTO.fourteenDaysRatio}</t>
+    <t>{.fourteenDaysRatio}</t>
   </si>
   <si>
-    <t>{.percentJsonDTO.thirtyDaysRatio}</t>
+    <t>{.thirtyDaysRatio}</t>
   </si>
   <si>
-    <t>{.percentJsonDTO.sixtyDaysRatio}</t>
+    <t>{.sixtyDaysRatio}</t>
   </si>
   <si>
-    <t>{.percentJsonDTO.ninetyDaysRatio}</t>
+    <t>{.ninetyDaysRatio}</t>
   </si>
   <si>
-    <t>{.percentJsonDTO.oneHundredEightyDaysRatio}</t>
+    <t>{.oneHundredEightyDaysRatio}</t>
   </si>
   <si>
-    <t>{.percentJsonDTO.twoHundredSeventyDaysRatio}</t>
+    <t>{.twoHundredSeventyDaysRatio}</t>
   </si>
   <si>
-    <t>{.percentJsonDTO.threeHundredSixtyDaysRatio}</t>
+    <t>{.threeHundredSixtyDaysRatio}</t>
   </si>
   <si>
     <r>
@@ -630,13 +630,13 @@
     </font>
     <font>
       <sz val="9.75"/>
-      <color rgb="FF000000"/>
+      <color rgb="FF1F2329"/>
       <name val="Calibri"/>
       <charset val="134"/>
     </font>
     <font>
       <sz val="9.75"/>
-      <color rgb="FF1F2329"/>
+      <color rgb="FF000000"/>
       <name val="Calibri"/>
       <charset val="134"/>
     </font>
@@ -8614,7 +8614,14 @@
   <dimension ref="A1:S186"/>
   <sheetFormatPr defaultColWidth="14" defaultRowHeight="12.75"/>
   <cols>
-    <col min="1" max="19" width="16" customWidth="1"/>
+    <col min="1" max="1" width="20.5714285714286" customWidth="1"/>
+    <col min="2" max="2" width="16" customWidth="1"/>
+    <col min="3" max="3" width="40.8571428571429" customWidth="1"/>
+    <col min="4" max="8" width="16" customWidth="1"/>
+    <col min="9" max="9" width="32.7142857142857" customWidth="1"/>
+    <col min="10" max="10" width="30.2857142857143" customWidth="1"/>
+    <col min="11" max="11" width="36" customWidth="1"/>
+    <col min="12" max="19" width="16" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:19">
@@ -11315,7 +11322,15 @@
   <dimension ref="A1:R186"/>
   <sheetFormatPr defaultColWidth="14" defaultRowHeight="12.75"/>
   <cols>
-    <col min="1" max="18" width="16" customWidth="1"/>
+    <col min="1" max="3" width="16" customWidth="1"/>
+    <col min="4" max="4" width="19.2857142857143" customWidth="1"/>
+    <col min="5" max="5" width="23.4285714285714" customWidth="1"/>
+    <col min="6" max="6" width="21.2857142857143" customWidth="1"/>
+    <col min="7" max="9" width="16" customWidth="1"/>
+    <col min="10" max="10" width="24" customWidth="1"/>
+    <col min="11" max="11" width="28.7142857142857" customWidth="1"/>
+    <col min="12" max="12" width="29" customWidth="1"/>
+    <col min="13" max="18" width="16" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:18">

--- a/erp-server/erp-server-file/src/main/resources/excel/mrp/salesCalc.xlsx
+++ b/erp-server/erp-server-file/src/main/resources/excel/mrp/salesCalc.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="12255" activeTab="3"/>
+    <workbookView windowWidth="28800" windowHeight="12255" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="1 - 历史销量 &amp; 去噪销量" sheetId="2" r:id="rId1"/>
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="134" uniqueCount="93">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="136" uniqueCount="95">
   <si>
     <t>SKU</t>
   </si>
@@ -145,6 +145,9 @@
     <t>近 360 日 累计销量</t>
   </si>
   <si>
+    <t>吻合度</t>
+  </si>
+  <si>
     <t>{.salesInfoEstimateType}</t>
   </si>
   <si>
@@ -206,6 +209,9 @@
   </si>
   <si>
     <t>{.threeHundredAndSixtySalesQty}</t>
+  </si>
+  <si>
+    <t>{.similarity}</t>
   </si>
   <si>
     <r>
@@ -4618,14 +4624,14 @@
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <dimension ref="A1:Y193"/>
+  <dimension ref="A1:Z193"/>
   <sheetFormatPr defaultColWidth="14" defaultRowHeight="12.75"/>
   <cols>
     <col min="1" max="3" width="16" customWidth="1"/>
     <col min="4" max="25" width="18" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:25">
+    <row r="1" spans="1:26">
       <c r="A1" s="13" t="s">
         <v>0</v>
       </c>
@@ -4701,8 +4707,11 @@
       <c r="Y1" s="13" t="s">
         <v>36</v>
       </c>
-    </row>
-    <row r="2" spans="1:25">
+      <c r="Z1" s="13" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="2" spans="1:26">
       <c r="A2" s="4" t="s">
         <v>8</v>
       </c>
@@ -4716,67 +4725,70 @@
         <v>11</v>
       </c>
       <c r="E2" s="4" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="F2" s="4" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="G2" s="4" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="H2" s="4" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="I2" s="4" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="J2" s="4" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="K2" s="4" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="L2" s="4" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="M2" s="4" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="N2" s="4" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="O2" s="4" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="P2" s="4" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="Q2" s="4" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="R2" s="4" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="S2" s="4" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="T2" s="4" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="U2" s="4" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="V2" s="4" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="W2" s="4" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="X2" s="4" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="Y2" s="4" t="s">
-        <v>57</v>
+        <v>58</v>
+      </c>
+      <c r="Z2" t="s">
+        <v>59</v>
       </c>
     </row>
     <row r="3" ht="19" customHeight="1" spans="1:25">
@@ -8626,13 +8638,13 @@
   <sheetData>
     <row r="1" spans="1:19">
       <c r="A1" s="1" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="B1" s="9" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="C1" s="10" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="D1" s="10"/>
       <c r="E1" s="10"/>
@@ -8655,31 +8667,31 @@
       <c r="A2" s="1"/>
       <c r="B2" s="9"/>
       <c r="C2" s="11" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="D2" s="11" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="E2" s="11" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="F2" s="11" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="G2" s="11" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="H2" s="11" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="I2" s="11" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="J2" s="11" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="K2" s="11" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="L2" s="3"/>
       <c r="M2" s="12"/>
@@ -8692,37 +8704,37 @@
     </row>
     <row r="3" spans="1:19">
       <c r="A3" s="4" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="C3" s="4" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="D3" s="4" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="E3" s="4" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="F3" s="4" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="G3" s="4" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="H3" s="4" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="I3" s="4" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="J3" s="4" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="K3" s="4" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="L3" s="3"/>
       <c r="M3" s="3"/>
@@ -11335,16 +11347,16 @@
   <sheetData>
     <row r="1" spans="1:18">
       <c r="A1" s="1" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="C1" s="2" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="E1" s="1"/>
       <c r="F1" s="1"/>
@@ -11366,31 +11378,31 @@
       <c r="B2" s="2"/>
       <c r="C2" s="2"/>
       <c r="D2" s="7" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="E2" s="7" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="F2" s="7" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="G2" s="7" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="H2" s="7" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="I2" s="7" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="J2" s="7" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="K2" s="7" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="L2" s="8" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="M2" s="3"/>
       <c r="N2" s="3"/>
@@ -11401,40 +11413,40 @@
     </row>
     <row r="3" spans="1:18">
       <c r="A3" s="4" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="C3" s="4" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="D3" s="4" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="E3" s="4" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="F3" s="4" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="G3" s="4" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="H3" s="4" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="I3" s="4" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="J3" s="4" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="K3" s="4" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="L3" s="4" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="M3" s="3"/>
       <c r="N3" s="3"/>
@@ -13855,16 +13867,16 @@
   <sheetData>
     <row r="1" spans="1:18">
       <c r="A1" s="1" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="C1" s="2" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="E1" s="6"/>
       <c r="F1" s="3"/>
@@ -13883,16 +13895,16 @@
     </row>
     <row r="2" spans="1:17">
       <c r="A2" s="4" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="C2" s="4" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="D2" s="4" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="J2" s="4"/>
       <c r="K2" s="4"/>
@@ -16086,22 +16098,22 @@
   <sheetData>
     <row r="1" spans="1:18">
       <c r="A1" s="1" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="C1" s="2" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="G1" s="3"/>
       <c r="H1" s="3"/>
@@ -16118,19 +16130,19 @@
     </row>
     <row r="2" spans="1:17">
       <c r="A2" s="4" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="C2" s="4" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="D2" s="4" t="s">
         <v>13</v>
       </c>
       <c r="E2" s="4" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="F2" s="4" t="s">
         <v>14</v>

--- a/erp-server/erp-server-file/src/main/resources/excel/mrp/salesCalc.xlsx
+++ b/erp-server/erp-server-file/src/main/resources/excel/mrp/salesCalc.xlsx
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="136" uniqueCount="95">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="134" uniqueCount="93">
   <si>
     <t>SKU</t>
   </si>
@@ -145,9 +145,6 @@
     <t>近 360 日 累计销量</t>
   </si>
   <si>
-    <t>吻合度</t>
-  </si>
-  <si>
     <t>{.salesInfoEstimateType}</t>
   </si>
   <si>
@@ -209,9 +206,6 @@
   </si>
   <si>
     <t>{.threeHundredAndSixtySalesQty}</t>
-  </si>
-  <si>
-    <t>{.similarity}</t>
   </si>
   <si>
     <r>
@@ -636,13 +630,13 @@
     </font>
     <font>
       <sz val="9.75"/>
-      <color rgb="FF1F2329"/>
+      <color rgb="FF000000"/>
       <name val="Calibri"/>
       <charset val="134"/>
     </font>
     <font>
       <sz val="9.75"/>
-      <color rgb="FF000000"/>
+      <color rgb="FF1F2329"/>
       <name val="Calibri"/>
       <charset val="134"/>
     </font>
@@ -4624,14 +4618,14 @@
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <dimension ref="A1:Z193"/>
+  <dimension ref="A1:Y193"/>
   <sheetFormatPr defaultColWidth="14" defaultRowHeight="12.75"/>
   <cols>
     <col min="1" max="3" width="16" customWidth="1"/>
     <col min="4" max="25" width="18" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:26">
+    <row r="1" spans="1:25">
       <c r="A1" s="13" t="s">
         <v>0</v>
       </c>
@@ -4707,11 +4701,8 @@
       <c r="Y1" s="13" t="s">
         <v>36</v>
       </c>
-      <c r="Z1" s="13" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="2" spans="1:26">
+    </row>
+    <row r="2" spans="1:25">
       <c r="A2" s="4" t="s">
         <v>8</v>
       </c>
@@ -4725,70 +4716,67 @@
         <v>11</v>
       </c>
       <c r="E2" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="F2" s="4" t="s">
         <v>38</v>
       </c>
-      <c r="F2" s="4" t="s">
+      <c r="G2" s="4" t="s">
         <v>39</v>
       </c>
-      <c r="G2" s="4" t="s">
+      <c r="H2" s="4" t="s">
         <v>40</v>
       </c>
-      <c r="H2" s="4" t="s">
+      <c r="I2" s="4" t="s">
         <v>41</v>
       </c>
-      <c r="I2" s="4" t="s">
+      <c r="J2" s="4" t="s">
         <v>42</v>
       </c>
-      <c r="J2" s="4" t="s">
+      <c r="K2" s="4" t="s">
         <v>43</v>
       </c>
-      <c r="K2" s="4" t="s">
+      <c r="L2" s="4" t="s">
         <v>44</v>
       </c>
-      <c r="L2" s="4" t="s">
+      <c r="M2" s="4" t="s">
         <v>45</v>
       </c>
-      <c r="M2" s="4" t="s">
+      <c r="N2" s="4" t="s">
         <v>46</v>
       </c>
-      <c r="N2" s="4" t="s">
+      <c r="O2" s="4" t="s">
         <v>47</v>
       </c>
-      <c r="O2" s="4" t="s">
+      <c r="P2" s="4" t="s">
         <v>48</v>
       </c>
-      <c r="P2" s="4" t="s">
+      <c r="Q2" s="4" t="s">
         <v>49</v>
       </c>
-      <c r="Q2" s="4" t="s">
+      <c r="R2" s="4" t="s">
         <v>50</v>
       </c>
-      <c r="R2" s="4" t="s">
+      <c r="S2" s="4" t="s">
         <v>51</v>
       </c>
-      <c r="S2" s="4" t="s">
+      <c r="T2" s="4" t="s">
         <v>52</v>
       </c>
-      <c r="T2" s="4" t="s">
+      <c r="U2" s="4" t="s">
         <v>53</v>
       </c>
-      <c r="U2" s="4" t="s">
+      <c r="V2" s="4" t="s">
         <v>54</v>
       </c>
-      <c r="V2" s="4" t="s">
+      <c r="W2" s="4" t="s">
         <v>55</v>
       </c>
-      <c r="W2" s="4" t="s">
+      <c r="X2" s="4" t="s">
         <v>56</v>
       </c>
-      <c r="X2" s="4" t="s">
+      <c r="Y2" s="4" t="s">
         <v>57</v>
-      </c>
-      <c r="Y2" s="4" t="s">
-        <v>58</v>
-      </c>
-      <c r="Z2" t="s">
-        <v>59</v>
       </c>
     </row>
     <row r="3" ht="19" customHeight="1" spans="1:25">
@@ -8638,13 +8626,13 @@
   <sheetData>
     <row r="1" spans="1:19">
       <c r="A1" s="1" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="B1" s="9" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="C1" s="10" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="D1" s="10"/>
       <c r="E1" s="10"/>
@@ -8667,31 +8655,31 @@
       <c r="A2" s="1"/>
       <c r="B2" s="9"/>
       <c r="C2" s="11" t="s">
+        <v>61</v>
+      </c>
+      <c r="D2" s="11" t="s">
+        <v>62</v>
+      </c>
+      <c r="E2" s="11" t="s">
         <v>63</v>
       </c>
-      <c r="D2" s="11" t="s">
+      <c r="F2" s="11" t="s">
         <v>64</v>
       </c>
-      <c r="E2" s="11" t="s">
+      <c r="G2" s="11" t="s">
         <v>65</v>
       </c>
-      <c r="F2" s="11" t="s">
+      <c r="H2" s="11" t="s">
         <v>66</v>
       </c>
-      <c r="G2" s="11" t="s">
+      <c r="I2" s="11" t="s">
         <v>67</v>
       </c>
-      <c r="H2" s="11" t="s">
+      <c r="J2" s="11" t="s">
         <v>68</v>
       </c>
-      <c r="I2" s="11" t="s">
+      <c r="K2" s="11" t="s">
         <v>69</v>
-      </c>
-      <c r="J2" s="11" t="s">
-        <v>70</v>
-      </c>
-      <c r="K2" s="11" t="s">
-        <v>71</v>
       </c>
       <c r="L2" s="3"/>
       <c r="M2" s="12"/>
@@ -8704,37 +8692,37 @@
     </row>
     <row r="3" spans="1:19">
       <c r="A3" s="4" t="s">
+        <v>70</v>
+      </c>
+      <c r="B3" s="4" t="s">
+        <v>71</v>
+      </c>
+      <c r="C3" s="4" t="s">
         <v>72</v>
       </c>
-      <c r="B3" s="4" t="s">
+      <c r="D3" s="4" t="s">
         <v>73</v>
       </c>
-      <c r="C3" s="4" t="s">
+      <c r="E3" s="4" t="s">
         <v>74</v>
       </c>
-      <c r="D3" s="4" t="s">
+      <c r="F3" s="4" t="s">
         <v>75</v>
       </c>
-      <c r="E3" s="4" t="s">
+      <c r="G3" s="4" t="s">
         <v>76</v>
       </c>
-      <c r="F3" s="4" t="s">
+      <c r="H3" s="4" t="s">
         <v>77</v>
       </c>
-      <c r="G3" s="4" t="s">
+      <c r="I3" s="4" t="s">
         <v>78</v>
       </c>
-      <c r="H3" s="4" t="s">
+      <c r="J3" s="4" t="s">
         <v>79</v>
       </c>
-      <c r="I3" s="4" t="s">
+      <c r="K3" s="4" t="s">
         <v>80</v>
-      </c>
-      <c r="J3" s="4" t="s">
-        <v>81</v>
-      </c>
-      <c r="K3" s="4" t="s">
-        <v>82</v>
       </c>
       <c r="L3" s="3"/>
       <c r="M3" s="3"/>
@@ -11347,16 +11335,16 @@
   <sheetData>
     <row r="1" spans="1:18">
       <c r="A1" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="C1" s="2" t="s">
         <v>83</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="D1" s="1" t="s">
         <v>84</v>
-      </c>
-      <c r="C1" s="2" t="s">
-        <v>85</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>86</v>
       </c>
       <c r="E1" s="1"/>
       <c r="F1" s="1"/>
@@ -11378,31 +11366,31 @@
       <c r="B2" s="2"/>
       <c r="C2" s="2"/>
       <c r="D2" s="7" t="s">
+        <v>61</v>
+      </c>
+      <c r="E2" s="7" t="s">
+        <v>62</v>
+      </c>
+      <c r="F2" s="7" t="s">
         <v>63</v>
       </c>
-      <c r="E2" s="7" t="s">
+      <c r="G2" s="7" t="s">
         <v>64</v>
       </c>
-      <c r="F2" s="7" t="s">
+      <c r="H2" s="7" t="s">
         <v>65</v>
       </c>
-      <c r="G2" s="7" t="s">
+      <c r="I2" s="7" t="s">
         <v>66</v>
       </c>
-      <c r="H2" s="7" t="s">
+      <c r="J2" s="7" t="s">
         <v>67</v>
       </c>
-      <c r="I2" s="7" t="s">
+      <c r="K2" s="7" t="s">
         <v>68</v>
       </c>
-      <c r="J2" s="7" t="s">
+      <c r="L2" s="8" t="s">
         <v>69</v>
-      </c>
-      <c r="K2" s="7" t="s">
-        <v>70</v>
-      </c>
-      <c r="L2" s="8" t="s">
-        <v>71</v>
       </c>
       <c r="M2" s="3"/>
       <c r="N2" s="3"/>
@@ -11413,40 +11401,40 @@
     </row>
     <row r="3" spans="1:18">
       <c r="A3" s="4" t="s">
+        <v>85</v>
+      </c>
+      <c r="B3" s="4" t="s">
+        <v>86</v>
+      </c>
+      <c r="C3" s="4" t="s">
         <v>87</v>
       </c>
-      <c r="B3" s="4" t="s">
-        <v>88</v>
+      <c r="D3" s="4" t="s">
+        <v>72</v>
       </c>
-      <c r="C3" s="4" t="s">
-        <v>89</v>
+      <c r="E3" s="4" t="s">
+        <v>73</v>
       </c>
-      <c r="D3" s="4" t="s">
+      <c r="F3" s="4" t="s">
         <v>74</v>
       </c>
-      <c r="E3" s="4" t="s">
+      <c r="G3" s="4" t="s">
         <v>75</v>
       </c>
-      <c r="F3" s="4" t="s">
+      <c r="H3" s="4" t="s">
         <v>76</v>
       </c>
-      <c r="G3" s="4" t="s">
+      <c r="I3" s="4" t="s">
         <v>77</v>
       </c>
-      <c r="H3" s="4" t="s">
+      <c r="J3" s="4" t="s">
         <v>78</v>
       </c>
-      <c r="I3" s="4" t="s">
+      <c r="K3" s="4" t="s">
         <v>79</v>
       </c>
-      <c r="J3" s="4" t="s">
+      <c r="L3" s="4" t="s">
         <v>80</v>
-      </c>
-      <c r="K3" s="4" t="s">
-        <v>81</v>
-      </c>
-      <c r="L3" s="4" t="s">
-        <v>82</v>
       </c>
       <c r="M3" s="3"/>
       <c r="N3" s="3"/>
@@ -13867,16 +13855,16 @@
   <sheetData>
     <row r="1" spans="1:18">
       <c r="A1" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="C1" s="2" t="s">
         <v>83</v>
       </c>
-      <c r="B1" s="2" t="s">
-        <v>84</v>
-      </c>
-      <c r="C1" s="2" t="s">
-        <v>85</v>
-      </c>
       <c r="D1" s="1" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="E1" s="6"/>
       <c r="F1" s="3"/>
@@ -13895,16 +13883,16 @@
     </row>
     <row r="2" spans="1:17">
       <c r="A2" s="4" t="s">
+        <v>85</v>
+      </c>
+      <c r="B2" s="4" t="s">
+        <v>86</v>
+      </c>
+      <c r="C2" s="4" t="s">
         <v>87</v>
       </c>
-      <c r="B2" s="4" t="s">
-        <v>88</v>
-      </c>
-      <c r="C2" s="4" t="s">
-        <v>89</v>
-      </c>
       <c r="D2" s="4" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="J2" s="4"/>
       <c r="K2" s="4"/>
@@ -16098,22 +16086,22 @@
   <sheetData>
     <row r="1" spans="1:18">
       <c r="A1" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="C1" s="2" t="s">
         <v>83</v>
       </c>
-      <c r="B1" s="2" t="s">
-        <v>84</v>
-      </c>
-      <c r="C1" s="2" t="s">
-        <v>85</v>
-      </c>
       <c r="D1" s="1" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="G1" s="3"/>
       <c r="H1" s="3"/>
@@ -16130,19 +16118,19 @@
     </row>
     <row r="2" spans="1:17">
       <c r="A2" s="4" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="C2" s="4" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="D2" s="4" t="s">
         <v>13</v>
       </c>
       <c r="E2" s="4" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="F2" s="4" t="s">
         <v>14</v>

--- a/erp-server/erp-server-file/src/main/resources/excel/mrp/salesCalc.xlsx
+++ b/erp-server/erp-server-file/src/main/resources/excel/mrp/salesCalc.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="12255" activeTab="1"/>
+    <workbookView windowWidth="27945" windowHeight="12255" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="1 - 历史销量 &amp; 去噪销量" sheetId="2" r:id="rId1"/>
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="134" uniqueCount="93">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="138" uniqueCount="97">
   <si>
     <t>SKU</t>
   </si>
@@ -89,6 +89,12 @@
   </si>
   <si>
     <t>预估日销量</t>
+  </si>
+  <si>
+    <t>实际日销量</t>
+  </si>
+  <si>
+    <t>偏差比例</t>
   </si>
   <si>
     <t>近 3 日 日均销量</t>
@@ -152,6 +158,12 @@
   </si>
   <si>
     <t>{.estimateQty}</t>
+  </si>
+  <si>
+    <t>{.realSalesQty}</t>
+  </si>
+  <si>
+    <t>{.deviationRatio}</t>
   </si>
   <si>
     <t>{.avgThreeSalesQty}</t>
@@ -442,7 +454,7 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="27">
+  <fonts count="28">
     <font>
       <sz val="10"/>
       <color theme="1"/>
@@ -467,6 +479,13 @@
     <font>
       <sz val="10.5"/>
       <color rgb="FF000000"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="9.75"/>
+      <color theme="1"/>
       <name val="等线"/>
       <charset val="134"/>
       <scheme val="minor"/>
@@ -630,18 +649,18 @@
     </font>
     <font>
       <sz val="9.75"/>
-      <color rgb="FF000000"/>
+      <color rgb="FF1F2329"/>
       <name val="Calibri"/>
       <charset val="134"/>
     </font>
     <font>
       <sz val="9.75"/>
-      <color rgb="FF1F2329"/>
+      <color rgb="FF000000"/>
       <name val="Calibri"/>
       <charset val="134"/>
     </font>
   </fonts>
-  <fills count="39">
+  <fills count="40">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -663,6 +682,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFFBA6B"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFF0000"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1008,31 +1033,28 @@
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyNumberFormat="0" applyFont="0" applyFill="0" applyBorder="0" applyProtection="0"/>
-    <xf numFmtId="43" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="43" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="44" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="44" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="9" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="9" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="41" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="41" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="42" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="42" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="8" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="9" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -1041,37 +1063,37 @@
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="9" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="10" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="10" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="10" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="11" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="11" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="11" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="12" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="10" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="10" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -1086,74 +1108,77 @@
     <xf numFmtId="0" fontId="23" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="23" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="23" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="23" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="23" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="23" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="38" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="38" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="39" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="21">
+  <cellXfs count="22">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -1199,19 +1224,22 @@
     <xf numFmtId="0" fontId="1" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="58" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -1561,19 +1589,19 @@
       <c r="C1" s="13" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="18" t="s">
+      <c r="D1" s="19" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="19" t="s">
+      <c r="E1" s="20" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="19" t="s">
+      <c r="F1" s="20" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="19" t="s">
+      <c r="G1" s="20" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="19" t="s">
+      <c r="H1" s="20" t="s">
         <v>7</v>
       </c>
     </row>
@@ -1646,7 +1674,7 @@
       <c r="E8" s="4"/>
     </row>
     <row r="9" spans="1:5">
-      <c r="A9" s="20"/>
+      <c r="A9" s="21"/>
       <c r="B9" s="4"/>
       <c r="C9" s="4"/>
       <c r="D9" s="4"/>
@@ -4618,14 +4646,14 @@
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <dimension ref="A1:Y193"/>
+  <dimension ref="A1:AA193"/>
   <sheetFormatPr defaultColWidth="14" defaultRowHeight="12.75"/>
   <cols>
     <col min="1" max="3" width="16" customWidth="1"/>
-    <col min="4" max="25" width="18" customWidth="1"/>
+    <col min="4" max="27" width="18" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:25">
+    <row r="1" spans="1:27">
       <c r="A1" s="13" t="s">
         <v>0</v>
       </c>
@@ -4653,31 +4681,31 @@
       <c r="I1" s="15" t="s">
         <v>20</v>
       </c>
-      <c r="J1" s="15" t="s">
+      <c r="J1" s="17" t="s">
         <v>21</v>
       </c>
-      <c r="K1" s="15" t="s">
+      <c r="K1" s="17" t="s">
         <v>22</v>
       </c>
-      <c r="L1" s="15" t="s">
+      <c r="L1" s="17" t="s">
         <v>23</v>
       </c>
-      <c r="M1" s="15" t="s">
+      <c r="M1" s="17" t="s">
         <v>24</v>
       </c>
-      <c r="N1" s="15" t="s">
+      <c r="N1" s="17" t="s">
         <v>25</v>
       </c>
-      <c r="O1" s="15" t="s">
+      <c r="O1" s="17" t="s">
         <v>26</v>
       </c>
-      <c r="P1" s="15" t="s">
+      <c r="P1" s="17" t="s">
         <v>27</v>
       </c>
-      <c r="Q1" s="13" t="s">
+      <c r="Q1" s="17" t="s">
         <v>28</v>
       </c>
-      <c r="R1" s="13" t="s">
+      <c r="R1" s="17" t="s">
         <v>29</v>
       </c>
       <c r="S1" s="13" t="s">
@@ -4701,8 +4729,14 @@
       <c r="Y1" s="13" t="s">
         <v>36</v>
       </c>
-    </row>
-    <row r="2" spans="1:25">
+      <c r="Z1" s="13" t="s">
+        <v>37</v>
+      </c>
+      <c r="AA1" s="13" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="2" spans="1:27">
       <c r="A2" s="4" t="s">
         <v>8</v>
       </c>
@@ -4716,70 +4750,76 @@
         <v>11</v>
       </c>
       <c r="E2" s="4" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="F2" s="4" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="G2" s="4" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="H2" s="4" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="I2" s="4" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="J2" s="4" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="K2" s="4" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="L2" s="4" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="M2" s="4" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="N2" s="4" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="O2" s="4" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="P2" s="4" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="Q2" s="4" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="R2" s="4" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="S2" s="4" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="T2" s="4" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="U2" s="4" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="V2" s="4" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="W2" s="4" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="X2" s="4" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="Y2" s="4" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
-    </row>
-    <row r="3" ht="19" customHeight="1" spans="1:25">
+      <c r="Z2" s="4" t="s">
+        <v>60</v>
+      </c>
+      <c r="AA2" s="4" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="3" ht="19" customHeight="1" spans="1:27">
       <c r="A3" s="4"/>
       <c r="B3" s="4"/>
       <c r="C3" s="4"/>
@@ -4789,8 +4829,8 @@
       <c r="G3" s="4"/>
       <c r="H3" s="4"/>
       <c r="I3" s="4"/>
-      <c r="Q3" s="4"/>
-      <c r="R3" s="4"/>
+      <c r="J3" s="4"/>
+      <c r="K3" s="4"/>
       <c r="S3" s="4"/>
       <c r="T3" s="4"/>
       <c r="U3" s="4"/>
@@ -4798,8 +4838,10 @@
       <c r="W3" s="4"/>
       <c r="X3" s="4"/>
       <c r="Y3" s="4"/>
-    </row>
-    <row r="4" spans="1:25">
+      <c r="Z3" s="4"/>
+      <c r="AA3" s="4"/>
+    </row>
+    <row r="4" spans="1:27">
       <c r="A4" s="4"/>
       <c r="B4" s="4"/>
       <c r="C4" s="4"/>
@@ -4809,8 +4851,8 @@
       <c r="G4" s="4"/>
       <c r="H4" s="4"/>
       <c r="I4" s="4"/>
-      <c r="Q4" s="4"/>
-      <c r="R4" s="4"/>
+      <c r="J4" s="4"/>
+      <c r="K4" s="4"/>
       <c r="S4" s="4"/>
       <c r="T4" s="4"/>
       <c r="U4" s="4"/>
@@ -4818,8 +4860,10 @@
       <c r="W4" s="4"/>
       <c r="X4" s="4"/>
       <c r="Y4" s="4"/>
-    </row>
-    <row r="5" spans="1:25">
+      <c r="Z4" s="4"/>
+      <c r="AA4" s="4"/>
+    </row>
+    <row r="5" spans="1:27">
       <c r="A5" s="4"/>
       <c r="B5" s="4"/>
       <c r="C5" s="4"/>
@@ -4829,17 +4873,19 @@
       <c r="G5" s="4"/>
       <c r="H5" s="4"/>
       <c r="I5" s="4"/>
-      <c r="Q5" s="4"/>
-      <c r="R5" s="4"/>
-      <c r="S5" s="17"/>
+      <c r="J5" s="4"/>
+      <c r="K5" s="4"/>
+      <c r="S5" s="4"/>
       <c r="T5" s="4"/>
-      <c r="U5" s="4"/>
+      <c r="U5" s="18"/>
       <c r="V5" s="4"/>
       <c r="W5" s="4"/>
       <c r="X5" s="4"/>
       <c r="Y5" s="4"/>
-    </row>
-    <row r="6" spans="1:25">
+      <c r="Z5" s="4"/>
+      <c r="AA5" s="4"/>
+    </row>
+    <row r="6" spans="1:27">
       <c r="A6" s="4"/>
       <c r="B6" s="4"/>
       <c r="C6" s="4"/>
@@ -4849,8 +4895,8 @@
       <c r="G6" s="4"/>
       <c r="H6" s="4"/>
       <c r="I6" s="4"/>
-      <c r="Q6" s="4"/>
-      <c r="R6" s="4"/>
+      <c r="J6" s="4"/>
+      <c r="K6" s="4"/>
       <c r="S6" s="4"/>
       <c r="T6" s="4"/>
       <c r="U6" s="4"/>
@@ -4858,8 +4904,10 @@
       <c r="W6" s="4"/>
       <c r="X6" s="4"/>
       <c r="Y6" s="4"/>
-    </row>
-    <row r="7" spans="1:25">
+      <c r="Z6" s="4"/>
+      <c r="AA6" s="4"/>
+    </row>
+    <row r="7" spans="1:27">
       <c r="A7" s="4"/>
       <c r="B7" s="4"/>
       <c r="C7" s="4"/>
@@ -4869,8 +4917,8 @@
       <c r="G7" s="4"/>
       <c r="H7" s="4"/>
       <c r="I7" s="4"/>
-      <c r="Q7" s="4"/>
-      <c r="R7" s="4"/>
+      <c r="J7" s="4"/>
+      <c r="K7" s="4"/>
       <c r="S7" s="4"/>
       <c r="T7" s="4"/>
       <c r="U7" s="4"/>
@@ -4878,8 +4926,10 @@
       <c r="W7" s="4"/>
       <c r="X7" s="4"/>
       <c r="Y7" s="4"/>
-    </row>
-    <row r="8" spans="1:25">
+      <c r="Z7" s="4"/>
+      <c r="AA7" s="4"/>
+    </row>
+    <row r="8" spans="1:27">
       <c r="A8" s="4"/>
       <c r="B8" s="4"/>
       <c r="C8" s="4"/>
@@ -4889,8 +4939,8 @@
       <c r="G8" s="4"/>
       <c r="H8" s="4"/>
       <c r="I8" s="4"/>
-      <c r="Q8" s="4"/>
-      <c r="R8" s="4"/>
+      <c r="J8" s="4"/>
+      <c r="K8" s="4"/>
       <c r="S8" s="4"/>
       <c r="T8" s="4"/>
       <c r="U8" s="4"/>
@@ -4898,8 +4948,10 @@
       <c r="W8" s="4"/>
       <c r="X8" s="4"/>
       <c r="Y8" s="4"/>
-    </row>
-    <row r="9" spans="1:25">
+      <c r="Z8" s="4"/>
+      <c r="AA8" s="4"/>
+    </row>
+    <row r="9" spans="1:27">
       <c r="A9" s="4"/>
       <c r="B9" s="4"/>
       <c r="C9" s="4"/>
@@ -4909,17 +4961,19 @@
       <c r="G9" s="4"/>
       <c r="H9" s="4"/>
       <c r="I9" s="4"/>
-      <c r="Q9" s="4"/>
-      <c r="R9" s="4"/>
-      <c r="S9" s="17"/>
+      <c r="J9" s="4"/>
+      <c r="K9" s="4"/>
+      <c r="S9" s="4"/>
       <c r="T9" s="4"/>
-      <c r="U9" s="4"/>
+      <c r="U9" s="18"/>
       <c r="V9" s="4"/>
       <c r="W9" s="4"/>
       <c r="X9" s="4"/>
       <c r="Y9" s="4"/>
-    </row>
-    <row r="10" spans="1:25">
+      <c r="Z9" s="4"/>
+      <c r="AA9" s="4"/>
+    </row>
+    <row r="10" spans="1:27">
       <c r="A10" s="4"/>
       <c r="B10" s="4"/>
       <c r="C10" s="4"/>
@@ -4929,8 +4983,8 @@
       <c r="G10" s="4"/>
       <c r="H10" s="4"/>
       <c r="I10" s="4"/>
-      <c r="Q10" s="4"/>
-      <c r="R10" s="4"/>
+      <c r="J10" s="4"/>
+      <c r="K10" s="4"/>
       <c r="S10" s="4"/>
       <c r="T10" s="4"/>
       <c r="U10" s="4"/>
@@ -4938,8 +4992,10 @@
       <c r="W10" s="4"/>
       <c r="X10" s="4"/>
       <c r="Y10" s="4"/>
-    </row>
-    <row r="11" spans="1:25">
+      <c r="Z10" s="4"/>
+      <c r="AA10" s="4"/>
+    </row>
+    <row r="11" spans="1:27">
       <c r="A11" s="4"/>
       <c r="B11" s="4"/>
       <c r="C11" s="4"/>
@@ -4949,8 +5005,8 @@
       <c r="G11" s="4"/>
       <c r="H11" s="4"/>
       <c r="I11" s="4"/>
-      <c r="Q11" s="4"/>
-      <c r="R11" s="4"/>
+      <c r="J11" s="4"/>
+      <c r="K11" s="4"/>
       <c r="S11" s="4"/>
       <c r="T11" s="4"/>
       <c r="U11" s="4"/>
@@ -4958,8 +5014,10 @@
       <c r="W11" s="4"/>
       <c r="X11" s="4"/>
       <c r="Y11" s="4"/>
-    </row>
-    <row r="12" spans="1:25">
+      <c r="Z11" s="4"/>
+      <c r="AA11" s="4"/>
+    </row>
+    <row r="12" spans="1:27">
       <c r="A12" s="4"/>
       <c r="B12" s="4"/>
       <c r="C12" s="4"/>
@@ -4969,8 +5027,8 @@
       <c r="G12" s="4"/>
       <c r="H12" s="4"/>
       <c r="I12" s="4"/>
-      <c r="Q12" s="4"/>
-      <c r="R12" s="4"/>
+      <c r="J12" s="4"/>
+      <c r="K12" s="4"/>
       <c r="S12" s="4"/>
       <c r="T12" s="4"/>
       <c r="U12" s="4"/>
@@ -4978,8 +5036,10 @@
       <c r="W12" s="4"/>
       <c r="X12" s="4"/>
       <c r="Y12" s="4"/>
-    </row>
-    <row r="13" spans="1:25">
+      <c r="Z12" s="4"/>
+      <c r="AA12" s="4"/>
+    </row>
+    <row r="13" spans="1:27">
       <c r="A13" s="4"/>
       <c r="B13" s="4"/>
       <c r="C13" s="4"/>
@@ -4989,8 +5049,8 @@
       <c r="G13" s="4"/>
       <c r="H13" s="4"/>
       <c r="I13" s="4"/>
-      <c r="Q13" s="4"/>
-      <c r="R13" s="4"/>
+      <c r="J13" s="4"/>
+      <c r="K13" s="4"/>
       <c r="S13" s="4"/>
       <c r="T13" s="4"/>
       <c r="U13" s="4"/>
@@ -4998,8 +5058,10 @@
       <c r="W13" s="4"/>
       <c r="X13" s="4"/>
       <c r="Y13" s="4"/>
-    </row>
-    <row r="14" spans="1:25">
+      <c r="Z13" s="4"/>
+      <c r="AA13" s="4"/>
+    </row>
+    <row r="14" spans="1:27">
       <c r="A14" s="4"/>
       <c r="B14" s="4"/>
       <c r="C14" s="4"/>
@@ -5009,8 +5071,8 @@
       <c r="G14" s="4"/>
       <c r="H14" s="4"/>
       <c r="I14" s="4"/>
-      <c r="Q14" s="4"/>
-      <c r="R14" s="4"/>
+      <c r="J14" s="4"/>
+      <c r="K14" s="4"/>
       <c r="S14" s="4"/>
       <c r="T14" s="4"/>
       <c r="U14" s="4"/>
@@ -5018,8 +5080,10 @@
       <c r="W14" s="4"/>
       <c r="X14" s="4"/>
       <c r="Y14" s="4"/>
-    </row>
-    <row r="15" spans="1:25">
+      <c r="Z14" s="4"/>
+      <c r="AA14" s="4"/>
+    </row>
+    <row r="15" spans="1:27">
       <c r="A15" s="4"/>
       <c r="B15" s="4"/>
       <c r="C15" s="4"/>
@@ -5029,8 +5093,8 @@
       <c r="G15" s="4"/>
       <c r="H15" s="4"/>
       <c r="I15" s="4"/>
-      <c r="Q15" s="4"/>
-      <c r="R15" s="4"/>
+      <c r="J15" s="4"/>
+      <c r="K15" s="4"/>
       <c r="S15" s="4"/>
       <c r="T15" s="4"/>
       <c r="U15" s="4"/>
@@ -5038,8 +5102,10 @@
       <c r="W15" s="4"/>
       <c r="X15" s="4"/>
       <c r="Y15" s="4"/>
-    </row>
-    <row r="16" spans="1:25">
+      <c r="Z15" s="4"/>
+      <c r="AA15" s="4"/>
+    </row>
+    <row r="16" spans="1:27">
       <c r="A16" s="4"/>
       <c r="B16" s="4"/>
       <c r="C16" s="4"/>
@@ -5049,8 +5115,8 @@
       <c r="G16" s="4"/>
       <c r="H16" s="4"/>
       <c r="I16" s="4"/>
-      <c r="Q16" s="4"/>
-      <c r="R16" s="4"/>
+      <c r="J16" s="4"/>
+      <c r="K16" s="4"/>
       <c r="S16" s="4"/>
       <c r="T16" s="4"/>
       <c r="U16" s="4"/>
@@ -5058,8 +5124,10 @@
       <c r="W16" s="4"/>
       <c r="X16" s="4"/>
       <c r="Y16" s="4"/>
-    </row>
-    <row r="17" spans="1:25">
+      <c r="Z16" s="4"/>
+      <c r="AA16" s="4"/>
+    </row>
+    <row r="17" spans="1:27">
       <c r="A17" s="4"/>
       <c r="B17" s="4"/>
       <c r="C17" s="4"/>
@@ -5069,8 +5137,8 @@
       <c r="G17" s="4"/>
       <c r="H17" s="4"/>
       <c r="I17" s="4"/>
-      <c r="Q17" s="4"/>
-      <c r="R17" s="4"/>
+      <c r="J17" s="4"/>
+      <c r="K17" s="4"/>
       <c r="S17" s="4"/>
       <c r="T17" s="4"/>
       <c r="U17" s="4"/>
@@ -5078,8 +5146,10 @@
       <c r="W17" s="4"/>
       <c r="X17" s="4"/>
       <c r="Y17" s="4"/>
-    </row>
-    <row r="18" spans="1:25">
+      <c r="Z17" s="4"/>
+      <c r="AA17" s="4"/>
+    </row>
+    <row r="18" spans="1:27">
       <c r="A18" s="4"/>
       <c r="B18" s="4"/>
       <c r="C18" s="4"/>
@@ -5089,8 +5159,8 @@
       <c r="G18" s="4"/>
       <c r="H18" s="4"/>
       <c r="I18" s="4"/>
-      <c r="Q18" s="4"/>
-      <c r="R18" s="4"/>
+      <c r="J18" s="4"/>
+      <c r="K18" s="4"/>
       <c r="S18" s="4"/>
       <c r="T18" s="4"/>
       <c r="U18" s="4"/>
@@ -5098,8 +5168,10 @@
       <c r="W18" s="4"/>
       <c r="X18" s="4"/>
       <c r="Y18" s="4"/>
-    </row>
-    <row r="19" spans="1:25">
+      <c r="Z18" s="4"/>
+      <c r="AA18" s="4"/>
+    </row>
+    <row r="19" spans="1:27">
       <c r="A19" s="4"/>
       <c r="B19" s="4"/>
       <c r="C19" s="4"/>
@@ -5109,8 +5181,8 @@
       <c r="G19" s="4"/>
       <c r="H19" s="4"/>
       <c r="I19" s="4"/>
-      <c r="Q19" s="4"/>
-      <c r="R19" s="4"/>
+      <c r="J19" s="4"/>
+      <c r="K19" s="4"/>
       <c r="S19" s="4"/>
       <c r="T19" s="4"/>
       <c r="U19" s="4"/>
@@ -5118,8 +5190,10 @@
       <c r="W19" s="4"/>
       <c r="X19" s="4"/>
       <c r="Y19" s="4"/>
-    </row>
-    <row r="20" spans="1:25">
+      <c r="Z19" s="4"/>
+      <c r="AA19" s="4"/>
+    </row>
+    <row r="20" spans="1:27">
       <c r="A20" s="4"/>
       <c r="B20" s="4"/>
       <c r="C20" s="4"/>
@@ -5129,8 +5203,8 @@
       <c r="G20" s="4"/>
       <c r="H20" s="4"/>
       <c r="I20" s="4"/>
-      <c r="Q20" s="4"/>
-      <c r="R20" s="4"/>
+      <c r="J20" s="4"/>
+      <c r="K20" s="4"/>
       <c r="S20" s="4"/>
       <c r="T20" s="4"/>
       <c r="U20" s="4"/>
@@ -5138,8 +5212,10 @@
       <c r="W20" s="4"/>
       <c r="X20" s="4"/>
       <c r="Y20" s="4"/>
-    </row>
-    <row r="21" spans="1:25">
+      <c r="Z20" s="4"/>
+      <c r="AA20" s="4"/>
+    </row>
+    <row r="21" spans="1:27">
       <c r="A21" s="4"/>
       <c r="B21" s="4"/>
       <c r="C21" s="4"/>
@@ -5149,8 +5225,8 @@
       <c r="G21" s="4"/>
       <c r="H21" s="4"/>
       <c r="I21" s="4"/>
-      <c r="Q21" s="4"/>
-      <c r="R21" s="4"/>
+      <c r="J21" s="4"/>
+      <c r="K21" s="4"/>
       <c r="S21" s="4"/>
       <c r="T21" s="4"/>
       <c r="U21" s="4"/>
@@ -5158,8 +5234,10 @@
       <c r="W21" s="4"/>
       <c r="X21" s="4"/>
       <c r="Y21" s="4"/>
-    </row>
-    <row r="22" spans="1:25">
+      <c r="Z21" s="4"/>
+      <c r="AA21" s="4"/>
+    </row>
+    <row r="22" spans="1:27">
       <c r="A22" s="4"/>
       <c r="B22" s="4"/>
       <c r="C22" s="4"/>
@@ -5169,8 +5247,8 @@
       <c r="G22" s="4"/>
       <c r="H22" s="4"/>
       <c r="I22" s="4"/>
-      <c r="Q22" s="4"/>
-      <c r="R22" s="4"/>
+      <c r="J22" s="4"/>
+      <c r="K22" s="4"/>
       <c r="S22" s="4"/>
       <c r="T22" s="4"/>
       <c r="U22" s="4"/>
@@ -5178,8 +5256,10 @@
       <c r="W22" s="4"/>
       <c r="X22" s="4"/>
       <c r="Y22" s="4"/>
-    </row>
-    <row r="23" spans="1:25">
+      <c r="Z22" s="4"/>
+      <c r="AA22" s="4"/>
+    </row>
+    <row r="23" spans="1:27">
       <c r="A23" s="4"/>
       <c r="B23" s="4"/>
       <c r="C23" s="4"/>
@@ -5189,8 +5269,8 @@
       <c r="G23" s="4"/>
       <c r="H23" s="4"/>
       <c r="I23" s="4"/>
-      <c r="Q23" s="4"/>
-      <c r="R23" s="4"/>
+      <c r="J23" s="4"/>
+      <c r="K23" s="4"/>
       <c r="S23" s="4"/>
       <c r="T23" s="4"/>
       <c r="U23" s="4"/>
@@ -5198,8 +5278,10 @@
       <c r="W23" s="4"/>
       <c r="X23" s="4"/>
       <c r="Y23" s="4"/>
-    </row>
-    <row r="24" spans="1:25">
+      <c r="Z23" s="4"/>
+      <c r="AA23" s="4"/>
+    </row>
+    <row r="24" spans="1:27">
       <c r="A24" s="4"/>
       <c r="B24" s="4"/>
       <c r="C24" s="4"/>
@@ -5209,8 +5291,8 @@
       <c r="G24" s="4"/>
       <c r="H24" s="4"/>
       <c r="I24" s="4"/>
-      <c r="Q24" s="4"/>
-      <c r="R24" s="4"/>
+      <c r="J24" s="4"/>
+      <c r="K24" s="4"/>
       <c r="S24" s="4"/>
       <c r="T24" s="4"/>
       <c r="U24" s="4"/>
@@ -5218,8 +5300,10 @@
       <c r="W24" s="4"/>
       <c r="X24" s="4"/>
       <c r="Y24" s="4"/>
-    </row>
-    <row r="25" spans="1:25">
+      <c r="Z24" s="4"/>
+      <c r="AA24" s="4"/>
+    </row>
+    <row r="25" spans="1:27">
       <c r="A25" s="4"/>
       <c r="B25" s="4"/>
       <c r="C25" s="4"/>
@@ -5229,8 +5313,8 @@
       <c r="G25" s="4"/>
       <c r="H25" s="4"/>
       <c r="I25" s="4"/>
-      <c r="Q25" s="4"/>
-      <c r="R25" s="4"/>
+      <c r="J25" s="4"/>
+      <c r="K25" s="4"/>
       <c r="S25" s="4"/>
       <c r="T25" s="4"/>
       <c r="U25" s="4"/>
@@ -5238,8 +5322,10 @@
       <c r="W25" s="4"/>
       <c r="X25" s="4"/>
       <c r="Y25" s="4"/>
-    </row>
-    <row r="26" spans="1:25">
+      <c r="Z25" s="4"/>
+      <c r="AA25" s="4"/>
+    </row>
+    <row r="26" spans="1:27">
       <c r="A26" s="4"/>
       <c r="B26" s="4"/>
       <c r="C26" s="4"/>
@@ -5249,8 +5335,8 @@
       <c r="G26" s="4"/>
       <c r="H26" s="4"/>
       <c r="I26" s="4"/>
-      <c r="Q26" s="4"/>
-      <c r="R26" s="4"/>
+      <c r="J26" s="4"/>
+      <c r="K26" s="4"/>
       <c r="S26" s="4"/>
       <c r="T26" s="4"/>
       <c r="U26" s="4"/>
@@ -5258,8 +5344,10 @@
       <c r="W26" s="4"/>
       <c r="X26" s="4"/>
       <c r="Y26" s="4"/>
-    </row>
-    <row r="27" spans="1:25">
+      <c r="Z26" s="4"/>
+      <c r="AA26" s="4"/>
+    </row>
+    <row r="27" spans="1:27">
       <c r="A27" s="4"/>
       <c r="B27" s="4"/>
       <c r="C27" s="4"/>
@@ -5269,8 +5357,8 @@
       <c r="G27" s="4"/>
       <c r="H27" s="4"/>
       <c r="I27" s="4"/>
-      <c r="Q27" s="4"/>
-      <c r="R27" s="4"/>
+      <c r="J27" s="4"/>
+      <c r="K27" s="4"/>
       <c r="S27" s="4"/>
       <c r="T27" s="4"/>
       <c r="U27" s="4"/>
@@ -5278,8 +5366,10 @@
       <c r="W27" s="4"/>
       <c r="X27" s="4"/>
       <c r="Y27" s="4"/>
-    </row>
-    <row r="28" spans="1:25">
+      <c r="Z27" s="4"/>
+      <c r="AA27" s="4"/>
+    </row>
+    <row r="28" spans="1:27">
       <c r="A28" s="4"/>
       <c r="B28" s="4"/>
       <c r="C28" s="4"/>
@@ -5289,8 +5379,8 @@
       <c r="G28" s="4"/>
       <c r="H28" s="4"/>
       <c r="I28" s="4"/>
-      <c r="Q28" s="4"/>
-      <c r="R28" s="4"/>
+      <c r="J28" s="4"/>
+      <c r="K28" s="4"/>
       <c r="S28" s="4"/>
       <c r="T28" s="4"/>
       <c r="U28" s="4"/>
@@ -5298,8 +5388,10 @@
       <c r="W28" s="4"/>
       <c r="X28" s="4"/>
       <c r="Y28" s="4"/>
-    </row>
-    <row r="29" spans="1:25">
+      <c r="Z28" s="4"/>
+      <c r="AA28" s="4"/>
+    </row>
+    <row r="29" spans="1:27">
       <c r="A29" s="4"/>
       <c r="B29" s="4"/>
       <c r="C29" s="4"/>
@@ -5309,8 +5401,8 @@
       <c r="G29" s="4"/>
       <c r="H29" s="4"/>
       <c r="I29" s="4"/>
-      <c r="Q29" s="4"/>
-      <c r="R29" s="4"/>
+      <c r="J29" s="4"/>
+      <c r="K29" s="4"/>
       <c r="S29" s="4"/>
       <c r="T29" s="4"/>
       <c r="U29" s="4"/>
@@ -5318,8 +5410,10 @@
       <c r="W29" s="4"/>
       <c r="X29" s="4"/>
       <c r="Y29" s="4"/>
-    </row>
-    <row r="30" spans="1:25">
+      <c r="Z29" s="4"/>
+      <c r="AA29" s="4"/>
+    </row>
+    <row r="30" spans="1:27">
       <c r="A30" s="4"/>
       <c r="B30" s="4"/>
       <c r="C30" s="4"/>
@@ -5329,8 +5423,8 @@
       <c r="G30" s="4"/>
       <c r="H30" s="4"/>
       <c r="I30" s="4"/>
-      <c r="Q30" s="4"/>
-      <c r="R30" s="4"/>
+      <c r="J30" s="4"/>
+      <c r="K30" s="4"/>
       <c r="S30" s="4"/>
       <c r="T30" s="4"/>
       <c r="U30" s="4"/>
@@ -5338,8 +5432,10 @@
       <c r="W30" s="4"/>
       <c r="X30" s="4"/>
       <c r="Y30" s="4"/>
-    </row>
-    <row r="31" spans="1:25">
+      <c r="Z30" s="4"/>
+      <c r="AA30" s="4"/>
+    </row>
+    <row r="31" spans="1:27">
       <c r="A31" s="4"/>
       <c r="B31" s="4"/>
       <c r="C31" s="4"/>
@@ -5349,8 +5445,8 @@
       <c r="G31" s="4"/>
       <c r="H31" s="4"/>
       <c r="I31" s="4"/>
-      <c r="Q31" s="4"/>
-      <c r="R31" s="4"/>
+      <c r="J31" s="4"/>
+      <c r="K31" s="4"/>
       <c r="S31" s="4"/>
       <c r="T31" s="4"/>
       <c r="U31" s="4"/>
@@ -5358,8 +5454,10 @@
       <c r="W31" s="4"/>
       <c r="X31" s="4"/>
       <c r="Y31" s="4"/>
-    </row>
-    <row r="32" spans="1:25">
+      <c r="Z31" s="4"/>
+      <c r="AA31" s="4"/>
+    </row>
+    <row r="32" spans="1:27">
       <c r="A32" s="4"/>
       <c r="B32" s="4"/>
       <c r="C32" s="4"/>
@@ -5369,8 +5467,8 @@
       <c r="G32" s="4"/>
       <c r="H32" s="4"/>
       <c r="I32" s="4"/>
-      <c r="Q32" s="4"/>
-      <c r="R32" s="4"/>
+      <c r="J32" s="4"/>
+      <c r="K32" s="4"/>
       <c r="S32" s="4"/>
       <c r="T32" s="4"/>
       <c r="U32" s="4"/>
@@ -5378,8 +5476,10 @@
       <c r="W32" s="4"/>
       <c r="X32" s="4"/>
       <c r="Y32" s="4"/>
-    </row>
-    <row r="33" spans="1:25">
+      <c r="Z32" s="4"/>
+      <c r="AA32" s="4"/>
+    </row>
+    <row r="33" spans="1:27">
       <c r="A33" s="4"/>
       <c r="B33" s="4"/>
       <c r="C33" s="4"/>
@@ -5389,8 +5489,8 @@
       <c r="G33" s="4"/>
       <c r="H33" s="4"/>
       <c r="I33" s="4"/>
-      <c r="Q33" s="4"/>
-      <c r="R33" s="4"/>
+      <c r="J33" s="4"/>
+      <c r="K33" s="4"/>
       <c r="S33" s="4"/>
       <c r="T33" s="4"/>
       <c r="U33" s="4"/>
@@ -5398,8 +5498,10 @@
       <c r="W33" s="4"/>
       <c r="X33" s="4"/>
       <c r="Y33" s="4"/>
-    </row>
-    <row r="34" spans="1:25">
+      <c r="Z33" s="4"/>
+      <c r="AA33" s="4"/>
+    </row>
+    <row r="34" spans="1:27">
       <c r="A34" s="4"/>
       <c r="B34" s="4"/>
       <c r="C34" s="4"/>
@@ -5409,8 +5511,8 @@
       <c r="G34" s="4"/>
       <c r="H34" s="4"/>
       <c r="I34" s="4"/>
-      <c r="Q34" s="4"/>
-      <c r="R34" s="4"/>
+      <c r="J34" s="4"/>
+      <c r="K34" s="4"/>
       <c r="S34" s="4"/>
       <c r="T34" s="4"/>
       <c r="U34" s="4"/>
@@ -5418,8 +5520,10 @@
       <c r="W34" s="4"/>
       <c r="X34" s="4"/>
       <c r="Y34" s="4"/>
-    </row>
-    <row r="35" spans="1:25">
+      <c r="Z34" s="4"/>
+      <c r="AA34" s="4"/>
+    </row>
+    <row r="35" spans="1:27">
       <c r="A35" s="4"/>
       <c r="B35" s="4"/>
       <c r="C35" s="4"/>
@@ -5429,8 +5533,8 @@
       <c r="G35" s="4"/>
       <c r="H35" s="4"/>
       <c r="I35" s="4"/>
-      <c r="Q35" s="4"/>
-      <c r="R35" s="4"/>
+      <c r="J35" s="4"/>
+      <c r="K35" s="4"/>
       <c r="S35" s="4"/>
       <c r="T35" s="4"/>
       <c r="U35" s="4"/>
@@ -5438,8 +5542,10 @@
       <c r="W35" s="4"/>
       <c r="X35" s="4"/>
       <c r="Y35" s="4"/>
-    </row>
-    <row r="36" spans="1:25">
+      <c r="Z35" s="4"/>
+      <c r="AA35" s="4"/>
+    </row>
+    <row r="36" spans="1:27">
       <c r="A36" s="4"/>
       <c r="B36" s="4"/>
       <c r="C36" s="4"/>
@@ -5449,8 +5555,8 @@
       <c r="G36" s="4"/>
       <c r="H36" s="4"/>
       <c r="I36" s="4"/>
-      <c r="Q36" s="4"/>
-      <c r="R36" s="4"/>
+      <c r="J36" s="4"/>
+      <c r="K36" s="4"/>
       <c r="S36" s="4"/>
       <c r="T36" s="4"/>
       <c r="U36" s="4"/>
@@ -5458,8 +5564,10 @@
       <c r="W36" s="4"/>
       <c r="X36" s="4"/>
       <c r="Y36" s="4"/>
-    </row>
-    <row r="37" spans="1:25">
+      <c r="Z36" s="4"/>
+      <c r="AA36" s="4"/>
+    </row>
+    <row r="37" spans="1:27">
       <c r="A37" s="4"/>
       <c r="B37" s="4"/>
       <c r="C37" s="4"/>
@@ -5469,8 +5577,8 @@
       <c r="G37" s="4"/>
       <c r="H37" s="4"/>
       <c r="I37" s="4"/>
-      <c r="Q37" s="4"/>
-      <c r="R37" s="4"/>
+      <c r="J37" s="4"/>
+      <c r="K37" s="4"/>
       <c r="S37" s="4"/>
       <c r="T37" s="4"/>
       <c r="U37" s="4"/>
@@ -5478,8 +5586,10 @@
       <c r="W37" s="4"/>
       <c r="X37" s="4"/>
       <c r="Y37" s="4"/>
-    </row>
-    <row r="38" spans="1:25">
+      <c r="Z37" s="4"/>
+      <c r="AA37" s="4"/>
+    </row>
+    <row r="38" spans="1:27">
       <c r="A38" s="4"/>
       <c r="B38" s="4"/>
       <c r="C38" s="4"/>
@@ -5489,8 +5599,8 @@
       <c r="G38" s="4"/>
       <c r="H38" s="4"/>
       <c r="I38" s="4"/>
-      <c r="Q38" s="4"/>
-      <c r="R38" s="4"/>
+      <c r="J38" s="4"/>
+      <c r="K38" s="4"/>
       <c r="S38" s="4"/>
       <c r="T38" s="4"/>
       <c r="U38" s="4"/>
@@ -5498,8 +5608,10 @@
       <c r="W38" s="4"/>
       <c r="X38" s="4"/>
       <c r="Y38" s="4"/>
-    </row>
-    <row r="39" spans="1:25">
+      <c r="Z38" s="4"/>
+      <c r="AA38" s="4"/>
+    </row>
+    <row r="39" spans="1:27">
       <c r="A39" s="4"/>
       <c r="B39" s="4"/>
       <c r="C39" s="4"/>
@@ -5509,8 +5621,8 @@
       <c r="G39" s="4"/>
       <c r="H39" s="4"/>
       <c r="I39" s="4"/>
-      <c r="Q39" s="4"/>
-      <c r="R39" s="4"/>
+      <c r="J39" s="4"/>
+      <c r="K39" s="4"/>
       <c r="S39" s="4"/>
       <c r="T39" s="4"/>
       <c r="U39" s="4"/>
@@ -5518,8 +5630,10 @@
       <c r="W39" s="4"/>
       <c r="X39" s="4"/>
       <c r="Y39" s="4"/>
-    </row>
-    <row r="40" spans="1:25">
+      <c r="Z39" s="4"/>
+      <c r="AA39" s="4"/>
+    </row>
+    <row r="40" spans="1:27">
       <c r="A40" s="4"/>
       <c r="B40" s="4"/>
       <c r="C40" s="4"/>
@@ -5529,8 +5643,8 @@
       <c r="G40" s="4"/>
       <c r="H40" s="4"/>
       <c r="I40" s="4"/>
-      <c r="Q40" s="4"/>
-      <c r="R40" s="4"/>
+      <c r="J40" s="4"/>
+      <c r="K40" s="4"/>
       <c r="S40" s="4"/>
       <c r="T40" s="4"/>
       <c r="U40" s="4"/>
@@ -5538,8 +5652,10 @@
       <c r="W40" s="4"/>
       <c r="X40" s="4"/>
       <c r="Y40" s="4"/>
-    </row>
-    <row r="41" spans="1:25">
+      <c r="Z40" s="4"/>
+      <c r="AA40" s="4"/>
+    </row>
+    <row r="41" spans="1:27">
       <c r="A41" s="4"/>
       <c r="B41" s="4"/>
       <c r="C41" s="4"/>
@@ -5549,8 +5665,8 @@
       <c r="G41" s="4"/>
       <c r="H41" s="4"/>
       <c r="I41" s="4"/>
-      <c r="Q41" s="4"/>
-      <c r="R41" s="4"/>
+      <c r="J41" s="4"/>
+      <c r="K41" s="4"/>
       <c r="S41" s="4"/>
       <c r="T41" s="4"/>
       <c r="U41" s="4"/>
@@ -5558,8 +5674,10 @@
       <c r="W41" s="4"/>
       <c r="X41" s="4"/>
       <c r="Y41" s="4"/>
-    </row>
-    <row r="42" spans="1:25">
+      <c r="Z41" s="4"/>
+      <c r="AA41" s="4"/>
+    </row>
+    <row r="42" spans="1:27">
       <c r="A42" s="4"/>
       <c r="B42" s="4"/>
       <c r="C42" s="4"/>
@@ -5569,8 +5687,8 @@
       <c r="G42" s="4"/>
       <c r="H42" s="4"/>
       <c r="I42" s="4"/>
-      <c r="Q42" s="4"/>
-      <c r="R42" s="4"/>
+      <c r="J42" s="4"/>
+      <c r="K42" s="4"/>
       <c r="S42" s="4"/>
       <c r="T42" s="4"/>
       <c r="U42" s="4"/>
@@ -5578,8 +5696,10 @@
       <c r="W42" s="4"/>
       <c r="X42" s="4"/>
       <c r="Y42" s="4"/>
-    </row>
-    <row r="43" spans="1:25">
+      <c r="Z42" s="4"/>
+      <c r="AA42" s="4"/>
+    </row>
+    <row r="43" spans="1:27">
       <c r="A43" s="4"/>
       <c r="B43" s="4"/>
       <c r="C43" s="4"/>
@@ -5589,8 +5709,8 @@
       <c r="G43" s="4"/>
       <c r="H43" s="4"/>
       <c r="I43" s="4"/>
-      <c r="Q43" s="4"/>
-      <c r="R43" s="4"/>
+      <c r="J43" s="4"/>
+      <c r="K43" s="4"/>
       <c r="S43" s="4"/>
       <c r="T43" s="4"/>
       <c r="U43" s="4"/>
@@ -5598,8 +5718,10 @@
       <c r="W43" s="4"/>
       <c r="X43" s="4"/>
       <c r="Y43" s="4"/>
-    </row>
-    <row r="44" spans="1:25">
+      <c r="Z43" s="4"/>
+      <c r="AA43" s="4"/>
+    </row>
+    <row r="44" spans="1:27">
       <c r="A44" s="4"/>
       <c r="B44" s="4"/>
       <c r="C44" s="4"/>
@@ -5609,8 +5731,8 @@
       <c r="G44" s="4"/>
       <c r="H44" s="4"/>
       <c r="I44" s="4"/>
-      <c r="Q44" s="4"/>
-      <c r="R44" s="4"/>
+      <c r="J44" s="4"/>
+      <c r="K44" s="4"/>
       <c r="S44" s="4"/>
       <c r="T44" s="4"/>
       <c r="U44" s="4"/>
@@ -5618,8 +5740,10 @@
       <c r="W44" s="4"/>
       <c r="X44" s="4"/>
       <c r="Y44" s="4"/>
-    </row>
-    <row r="45" spans="1:25">
+      <c r="Z44" s="4"/>
+      <c r="AA44" s="4"/>
+    </row>
+    <row r="45" spans="1:27">
       <c r="A45" s="4"/>
       <c r="B45" s="4"/>
       <c r="C45" s="4"/>
@@ -5629,8 +5753,8 @@
       <c r="G45" s="4"/>
       <c r="H45" s="4"/>
       <c r="I45" s="4"/>
-      <c r="Q45" s="4"/>
-      <c r="R45" s="4"/>
+      <c r="J45" s="4"/>
+      <c r="K45" s="4"/>
       <c r="S45" s="4"/>
       <c r="T45" s="4"/>
       <c r="U45" s="4"/>
@@ -5638,8 +5762,10 @@
       <c r="W45" s="4"/>
       <c r="X45" s="4"/>
       <c r="Y45" s="4"/>
-    </row>
-    <row r="46" spans="1:25">
+      <c r="Z45" s="4"/>
+      <c r="AA45" s="4"/>
+    </row>
+    <row r="46" spans="1:27">
       <c r="A46" s="4"/>
       <c r="B46" s="4"/>
       <c r="C46" s="4"/>
@@ -5649,8 +5775,8 @@
       <c r="G46" s="4"/>
       <c r="H46" s="4"/>
       <c r="I46" s="4"/>
-      <c r="Q46" s="4"/>
-      <c r="R46" s="4"/>
+      <c r="J46" s="4"/>
+      <c r="K46" s="4"/>
       <c r="S46" s="4"/>
       <c r="T46" s="4"/>
       <c r="U46" s="4"/>
@@ -5658,8 +5784,10 @@
       <c r="W46" s="4"/>
       <c r="X46" s="4"/>
       <c r="Y46" s="4"/>
-    </row>
-    <row r="47" spans="1:25">
+      <c r="Z46" s="4"/>
+      <c r="AA46" s="4"/>
+    </row>
+    <row r="47" spans="1:27">
       <c r="A47" s="4"/>
       <c r="B47" s="4"/>
       <c r="C47" s="4"/>
@@ -5669,8 +5797,8 @@
       <c r="G47" s="4"/>
       <c r="H47" s="4"/>
       <c r="I47" s="4"/>
-      <c r="Q47" s="4"/>
-      <c r="R47" s="4"/>
+      <c r="J47" s="4"/>
+      <c r="K47" s="4"/>
       <c r="S47" s="4"/>
       <c r="T47" s="4"/>
       <c r="U47" s="4"/>
@@ -5678,8 +5806,10 @@
       <c r="W47" s="4"/>
       <c r="X47" s="4"/>
       <c r="Y47" s="4"/>
-    </row>
-    <row r="48" spans="1:25">
+      <c r="Z47" s="4"/>
+      <c r="AA47" s="4"/>
+    </row>
+    <row r="48" spans="1:27">
       <c r="A48" s="4"/>
       <c r="B48" s="4"/>
       <c r="C48" s="4"/>
@@ -5689,8 +5819,8 @@
       <c r="G48" s="4"/>
       <c r="H48" s="4"/>
       <c r="I48" s="4"/>
-      <c r="Q48" s="4"/>
-      <c r="R48" s="4"/>
+      <c r="J48" s="4"/>
+      <c r="K48" s="4"/>
       <c r="S48" s="4"/>
       <c r="T48" s="4"/>
       <c r="U48" s="4"/>
@@ -5698,8 +5828,10 @@
       <c r="W48" s="4"/>
       <c r="X48" s="4"/>
       <c r="Y48" s="4"/>
-    </row>
-    <row r="49" spans="1:25">
+      <c r="Z48" s="4"/>
+      <c r="AA48" s="4"/>
+    </row>
+    <row r="49" spans="1:27">
       <c r="A49" s="4"/>
       <c r="B49" s="4"/>
       <c r="C49" s="4"/>
@@ -5709,8 +5841,8 @@
       <c r="G49" s="4"/>
       <c r="H49" s="4"/>
       <c r="I49" s="4"/>
-      <c r="Q49" s="4"/>
-      <c r="R49" s="4"/>
+      <c r="J49" s="4"/>
+      <c r="K49" s="4"/>
       <c r="S49" s="4"/>
       <c r="T49" s="4"/>
       <c r="U49" s="4"/>
@@ -5718,8 +5850,10 @@
       <c r="W49" s="4"/>
       <c r="X49" s="4"/>
       <c r="Y49" s="4"/>
-    </row>
-    <row r="50" spans="1:25">
+      <c r="Z49" s="4"/>
+      <c r="AA49" s="4"/>
+    </row>
+    <row r="50" spans="1:27">
       <c r="A50" s="4"/>
       <c r="B50" s="4"/>
       <c r="C50" s="4"/>
@@ -5729,8 +5863,8 @@
       <c r="G50" s="4"/>
       <c r="H50" s="4"/>
       <c r="I50" s="4"/>
-      <c r="Q50" s="4"/>
-      <c r="R50" s="4"/>
+      <c r="J50" s="4"/>
+      <c r="K50" s="4"/>
       <c r="S50" s="4"/>
       <c r="T50" s="4"/>
       <c r="U50" s="4"/>
@@ -5738,8 +5872,10 @@
       <c r="W50" s="4"/>
       <c r="X50" s="4"/>
       <c r="Y50" s="4"/>
-    </row>
-    <row r="51" spans="1:25">
+      <c r="Z50" s="4"/>
+      <c r="AA50" s="4"/>
+    </row>
+    <row r="51" spans="1:27">
       <c r="A51" s="4"/>
       <c r="B51" s="4"/>
       <c r="C51" s="4"/>
@@ -5749,8 +5885,8 @@
       <c r="G51" s="4"/>
       <c r="H51" s="4"/>
       <c r="I51" s="4"/>
-      <c r="Q51" s="4"/>
-      <c r="R51" s="4"/>
+      <c r="J51" s="4"/>
+      <c r="K51" s="4"/>
       <c r="S51" s="4"/>
       <c r="T51" s="4"/>
       <c r="U51" s="4"/>
@@ -5758,8 +5894,10 @@
       <c r="W51" s="4"/>
       <c r="X51" s="4"/>
       <c r="Y51" s="4"/>
-    </row>
-    <row r="52" spans="1:25">
+      <c r="Z51" s="4"/>
+      <c r="AA51" s="4"/>
+    </row>
+    <row r="52" spans="1:27">
       <c r="A52" s="4"/>
       <c r="B52" s="4"/>
       <c r="C52" s="4"/>
@@ -5769,8 +5907,8 @@
       <c r="G52" s="4"/>
       <c r="H52" s="4"/>
       <c r="I52" s="4"/>
-      <c r="Q52" s="4"/>
-      <c r="R52" s="4"/>
+      <c r="J52" s="4"/>
+      <c r="K52" s="4"/>
       <c r="S52" s="4"/>
       <c r="T52" s="4"/>
       <c r="U52" s="4"/>
@@ -5778,8 +5916,10 @@
       <c r="W52" s="4"/>
       <c r="X52" s="4"/>
       <c r="Y52" s="4"/>
-    </row>
-    <row r="53" spans="1:25">
+      <c r="Z52" s="4"/>
+      <c r="AA52" s="4"/>
+    </row>
+    <row r="53" spans="1:27">
       <c r="A53" s="4"/>
       <c r="B53" s="4"/>
       <c r="C53" s="4"/>
@@ -5789,8 +5929,8 @@
       <c r="G53" s="4"/>
       <c r="H53" s="4"/>
       <c r="I53" s="4"/>
-      <c r="Q53" s="4"/>
-      <c r="R53" s="4"/>
+      <c r="J53" s="4"/>
+      <c r="K53" s="4"/>
       <c r="S53" s="4"/>
       <c r="T53" s="4"/>
       <c r="U53" s="4"/>
@@ -5798,8 +5938,10 @@
       <c r="W53" s="4"/>
       <c r="X53" s="4"/>
       <c r="Y53" s="4"/>
-    </row>
-    <row r="54" spans="1:25">
+      <c r="Z53" s="4"/>
+      <c r="AA53" s="4"/>
+    </row>
+    <row r="54" spans="1:27">
       <c r="A54" s="4"/>
       <c r="B54" s="4"/>
       <c r="C54" s="4"/>
@@ -5809,8 +5951,8 @@
       <c r="G54" s="4"/>
       <c r="H54" s="4"/>
       <c r="I54" s="4"/>
-      <c r="Q54" s="4"/>
-      <c r="R54" s="4"/>
+      <c r="J54" s="4"/>
+      <c r="K54" s="4"/>
       <c r="S54" s="4"/>
       <c r="T54" s="4"/>
       <c r="U54" s="4"/>
@@ -5818,8 +5960,10 @@
       <c r="W54" s="4"/>
       <c r="X54" s="4"/>
       <c r="Y54" s="4"/>
-    </row>
-    <row r="55" spans="1:25">
+      <c r="Z54" s="4"/>
+      <c r="AA54" s="4"/>
+    </row>
+    <row r="55" spans="1:27">
       <c r="A55" s="4"/>
       <c r="B55" s="4"/>
       <c r="C55" s="4"/>
@@ -5829,8 +5973,8 @@
       <c r="G55" s="4"/>
       <c r="H55" s="4"/>
       <c r="I55" s="4"/>
-      <c r="Q55" s="4"/>
-      <c r="R55" s="4"/>
+      <c r="J55" s="4"/>
+      <c r="K55" s="4"/>
       <c r="S55" s="4"/>
       <c r="T55" s="4"/>
       <c r="U55" s="4"/>
@@ -5838,8 +5982,10 @@
       <c r="W55" s="4"/>
       <c r="X55" s="4"/>
       <c r="Y55" s="4"/>
-    </row>
-    <row r="56" spans="1:25">
+      <c r="Z55" s="4"/>
+      <c r="AA55" s="4"/>
+    </row>
+    <row r="56" spans="1:27">
       <c r="A56" s="4"/>
       <c r="B56" s="4"/>
       <c r="C56" s="4"/>
@@ -5849,8 +5995,8 @@
       <c r="G56" s="4"/>
       <c r="H56" s="4"/>
       <c r="I56" s="4"/>
-      <c r="Q56" s="4"/>
-      <c r="R56" s="4"/>
+      <c r="J56" s="4"/>
+      <c r="K56" s="4"/>
       <c r="S56" s="4"/>
       <c r="T56" s="4"/>
       <c r="U56" s="4"/>
@@ -5858,8 +6004,10 @@
       <c r="W56" s="4"/>
       <c r="X56" s="4"/>
       <c r="Y56" s="4"/>
-    </row>
-    <row r="57" spans="1:25">
+      <c r="Z56" s="4"/>
+      <c r="AA56" s="4"/>
+    </row>
+    <row r="57" spans="1:27">
       <c r="A57" s="4"/>
       <c r="B57" s="4"/>
       <c r="C57" s="4"/>
@@ -5869,8 +6017,8 @@
       <c r="G57" s="4"/>
       <c r="H57" s="4"/>
       <c r="I57" s="4"/>
-      <c r="Q57" s="4"/>
-      <c r="R57" s="4"/>
+      <c r="J57" s="4"/>
+      <c r="K57" s="4"/>
       <c r="S57" s="4"/>
       <c r="T57" s="4"/>
       <c r="U57" s="4"/>
@@ -5878,8 +6026,10 @@
       <c r="W57" s="4"/>
       <c r="X57" s="4"/>
       <c r="Y57" s="4"/>
-    </row>
-    <row r="58" spans="1:25">
+      <c r="Z57" s="4"/>
+      <c r="AA57" s="4"/>
+    </row>
+    <row r="58" spans="1:27">
       <c r="A58" s="4"/>
       <c r="B58" s="4"/>
       <c r="C58" s="4"/>
@@ -5889,8 +6039,8 @@
       <c r="G58" s="4"/>
       <c r="H58" s="4"/>
       <c r="I58" s="4"/>
-      <c r="Q58" s="4"/>
-      <c r="R58" s="4"/>
+      <c r="J58" s="4"/>
+      <c r="K58" s="4"/>
       <c r="S58" s="4"/>
       <c r="T58" s="4"/>
       <c r="U58" s="4"/>
@@ -5898,8 +6048,10 @@
       <c r="W58" s="4"/>
       <c r="X58" s="4"/>
       <c r="Y58" s="4"/>
-    </row>
-    <row r="59" spans="1:25">
+      <c r="Z58" s="4"/>
+      <c r="AA58" s="4"/>
+    </row>
+    <row r="59" spans="1:27">
       <c r="A59" s="4"/>
       <c r="B59" s="4"/>
       <c r="C59" s="4"/>
@@ -5909,8 +6061,8 @@
       <c r="G59" s="4"/>
       <c r="H59" s="4"/>
       <c r="I59" s="4"/>
-      <c r="Q59" s="4"/>
-      <c r="R59" s="4"/>
+      <c r="J59" s="4"/>
+      <c r="K59" s="4"/>
       <c r="S59" s="4"/>
       <c r="T59" s="4"/>
       <c r="U59" s="4"/>
@@ -5918,8 +6070,10 @@
       <c r="W59" s="4"/>
       <c r="X59" s="4"/>
       <c r="Y59" s="4"/>
-    </row>
-    <row r="60" spans="1:25">
+      <c r="Z59" s="4"/>
+      <c r="AA59" s="4"/>
+    </row>
+    <row r="60" spans="1:27">
       <c r="A60" s="4"/>
       <c r="B60" s="4"/>
       <c r="C60" s="4"/>
@@ -5929,8 +6083,8 @@
       <c r="G60" s="4"/>
       <c r="H60" s="4"/>
       <c r="I60" s="4"/>
-      <c r="Q60" s="4"/>
-      <c r="R60" s="4"/>
+      <c r="J60" s="4"/>
+      <c r="K60" s="4"/>
       <c r="S60" s="4"/>
       <c r="T60" s="4"/>
       <c r="U60" s="4"/>
@@ -5938,8 +6092,10 @@
       <c r="W60" s="4"/>
       <c r="X60" s="4"/>
       <c r="Y60" s="4"/>
-    </row>
-    <row r="61" spans="1:25">
+      <c r="Z60" s="4"/>
+      <c r="AA60" s="4"/>
+    </row>
+    <row r="61" spans="1:27">
       <c r="A61" s="4"/>
       <c r="B61" s="4"/>
       <c r="C61" s="4"/>
@@ -5949,8 +6105,8 @@
       <c r="G61" s="4"/>
       <c r="H61" s="4"/>
       <c r="I61" s="4"/>
-      <c r="Q61" s="4"/>
-      <c r="R61" s="4"/>
+      <c r="J61" s="4"/>
+      <c r="K61" s="4"/>
       <c r="S61" s="4"/>
       <c r="T61" s="4"/>
       <c r="U61" s="4"/>
@@ -5958,8 +6114,10 @@
       <c r="W61" s="4"/>
       <c r="X61" s="4"/>
       <c r="Y61" s="4"/>
-    </row>
-    <row r="62" spans="1:25">
+      <c r="Z61" s="4"/>
+      <c r="AA61" s="4"/>
+    </row>
+    <row r="62" spans="1:27">
       <c r="A62" s="4"/>
       <c r="B62" s="4"/>
       <c r="C62" s="4"/>
@@ -5969,8 +6127,8 @@
       <c r="G62" s="4"/>
       <c r="H62" s="4"/>
       <c r="I62" s="4"/>
-      <c r="Q62" s="4"/>
-      <c r="R62" s="4"/>
+      <c r="J62" s="4"/>
+      <c r="K62" s="4"/>
       <c r="S62" s="4"/>
       <c r="T62" s="4"/>
       <c r="U62" s="4"/>
@@ -5978,8 +6136,10 @@
       <c r="W62" s="4"/>
       <c r="X62" s="4"/>
       <c r="Y62" s="4"/>
-    </row>
-    <row r="63" spans="1:25">
+      <c r="Z62" s="4"/>
+      <c r="AA62" s="4"/>
+    </row>
+    <row r="63" spans="1:27">
       <c r="A63" s="4"/>
       <c r="B63" s="4"/>
       <c r="C63" s="4"/>
@@ -5989,8 +6149,8 @@
       <c r="G63" s="4"/>
       <c r="H63" s="4"/>
       <c r="I63" s="4"/>
-      <c r="Q63" s="4"/>
-      <c r="R63" s="4"/>
+      <c r="J63" s="4"/>
+      <c r="K63" s="4"/>
       <c r="S63" s="4"/>
       <c r="T63" s="4"/>
       <c r="U63" s="4"/>
@@ -5998,8 +6158,10 @@
       <c r="W63" s="4"/>
       <c r="X63" s="4"/>
       <c r="Y63" s="4"/>
-    </row>
-    <row r="64" spans="1:25">
+      <c r="Z63" s="4"/>
+      <c r="AA63" s="4"/>
+    </row>
+    <row r="64" spans="1:27">
       <c r="A64" s="4"/>
       <c r="B64" s="4"/>
       <c r="C64" s="4"/>
@@ -6009,8 +6171,8 @@
       <c r="G64" s="4"/>
       <c r="H64" s="4"/>
       <c r="I64" s="4"/>
-      <c r="Q64" s="4"/>
-      <c r="R64" s="4"/>
+      <c r="J64" s="4"/>
+      <c r="K64" s="4"/>
       <c r="S64" s="4"/>
       <c r="T64" s="4"/>
       <c r="U64" s="4"/>
@@ -6018,8 +6180,10 @@
       <c r="W64" s="4"/>
       <c r="X64" s="4"/>
       <c r="Y64" s="4"/>
-    </row>
-    <row r="65" spans="1:25">
+      <c r="Z64" s="4"/>
+      <c r="AA64" s="4"/>
+    </row>
+    <row r="65" spans="1:27">
       <c r="A65" s="4"/>
       <c r="B65" s="4"/>
       <c r="C65" s="4"/>
@@ -6029,8 +6193,8 @@
       <c r="G65" s="4"/>
       <c r="H65" s="4"/>
       <c r="I65" s="4"/>
-      <c r="Q65" s="4"/>
-      <c r="R65" s="4"/>
+      <c r="J65" s="4"/>
+      <c r="K65" s="4"/>
       <c r="S65" s="4"/>
       <c r="T65" s="4"/>
       <c r="U65" s="4"/>
@@ -6038,8 +6202,10 @@
       <c r="W65" s="4"/>
       <c r="X65" s="4"/>
       <c r="Y65" s="4"/>
-    </row>
-    <row r="66" spans="1:25">
+      <c r="Z65" s="4"/>
+      <c r="AA65" s="4"/>
+    </row>
+    <row r="66" spans="1:27">
       <c r="A66" s="4"/>
       <c r="B66" s="4"/>
       <c r="C66" s="4"/>
@@ -6049,8 +6215,8 @@
       <c r="G66" s="4"/>
       <c r="H66" s="4"/>
       <c r="I66" s="4"/>
-      <c r="Q66" s="4"/>
-      <c r="R66" s="4"/>
+      <c r="J66" s="4"/>
+      <c r="K66" s="4"/>
       <c r="S66" s="4"/>
       <c r="T66" s="4"/>
       <c r="U66" s="4"/>
@@ -6058,8 +6224,10 @@
       <c r="W66" s="4"/>
       <c r="X66" s="4"/>
       <c r="Y66" s="4"/>
-    </row>
-    <row r="67" spans="1:25">
+      <c r="Z66" s="4"/>
+      <c r="AA66" s="4"/>
+    </row>
+    <row r="67" spans="1:27">
       <c r="A67" s="4"/>
       <c r="B67" s="4"/>
       <c r="C67" s="4"/>
@@ -6069,8 +6237,8 @@
       <c r="G67" s="4"/>
       <c r="H67" s="4"/>
       <c r="I67" s="4"/>
-      <c r="Q67" s="4"/>
-      <c r="R67" s="4"/>
+      <c r="J67" s="4"/>
+      <c r="K67" s="4"/>
       <c r="S67" s="4"/>
       <c r="T67" s="4"/>
       <c r="U67" s="4"/>
@@ -6078,8 +6246,10 @@
       <c r="W67" s="4"/>
       <c r="X67" s="4"/>
       <c r="Y67" s="4"/>
-    </row>
-    <row r="68" spans="1:25">
+      <c r="Z67" s="4"/>
+      <c r="AA67" s="4"/>
+    </row>
+    <row r="68" spans="1:27">
       <c r="A68" s="4"/>
       <c r="B68" s="4"/>
       <c r="C68" s="4"/>
@@ -6089,8 +6259,8 @@
       <c r="G68" s="4"/>
       <c r="H68" s="4"/>
       <c r="I68" s="4"/>
-      <c r="Q68" s="4"/>
-      <c r="R68" s="4"/>
+      <c r="J68" s="4"/>
+      <c r="K68" s="4"/>
       <c r="S68" s="4"/>
       <c r="T68" s="4"/>
       <c r="U68" s="4"/>
@@ -6098,8 +6268,10 @@
       <c r="W68" s="4"/>
       <c r="X68" s="4"/>
       <c r="Y68" s="4"/>
-    </row>
-    <row r="69" spans="1:25">
+      <c r="Z68" s="4"/>
+      <c r="AA68" s="4"/>
+    </row>
+    <row r="69" spans="1:27">
       <c r="A69" s="4"/>
       <c r="B69" s="4"/>
       <c r="C69" s="4"/>
@@ -6109,8 +6281,8 @@
       <c r="G69" s="4"/>
       <c r="H69" s="4"/>
       <c r="I69" s="4"/>
-      <c r="Q69" s="4"/>
-      <c r="R69" s="4"/>
+      <c r="J69" s="4"/>
+      <c r="K69" s="4"/>
       <c r="S69" s="4"/>
       <c r="T69" s="4"/>
       <c r="U69" s="4"/>
@@ -6118,8 +6290,10 @@
       <c r="W69" s="4"/>
       <c r="X69" s="4"/>
       <c r="Y69" s="4"/>
-    </row>
-    <row r="70" spans="1:25">
+      <c r="Z69" s="4"/>
+      <c r="AA69" s="4"/>
+    </row>
+    <row r="70" spans="1:27">
       <c r="A70" s="4"/>
       <c r="B70" s="4"/>
       <c r="C70" s="4"/>
@@ -6129,8 +6303,8 @@
       <c r="G70" s="4"/>
       <c r="H70" s="4"/>
       <c r="I70" s="4"/>
-      <c r="Q70" s="4"/>
-      <c r="R70" s="4"/>
+      <c r="J70" s="4"/>
+      <c r="K70" s="4"/>
       <c r="S70" s="4"/>
       <c r="T70" s="4"/>
       <c r="U70" s="4"/>
@@ -6138,8 +6312,10 @@
       <c r="W70" s="4"/>
       <c r="X70" s="4"/>
       <c r="Y70" s="4"/>
-    </row>
-    <row r="71" spans="1:25">
+      <c r="Z70" s="4"/>
+      <c r="AA70" s="4"/>
+    </row>
+    <row r="71" spans="1:27">
       <c r="A71" s="4"/>
       <c r="B71" s="4"/>
       <c r="C71" s="4"/>
@@ -6149,8 +6325,8 @@
       <c r="G71" s="4"/>
       <c r="H71" s="4"/>
       <c r="I71" s="4"/>
-      <c r="Q71" s="4"/>
-      <c r="R71" s="4"/>
+      <c r="J71" s="4"/>
+      <c r="K71" s="4"/>
       <c r="S71" s="4"/>
       <c r="T71" s="4"/>
       <c r="U71" s="4"/>
@@ -6158,8 +6334,10 @@
       <c r="W71" s="4"/>
       <c r="X71" s="4"/>
       <c r="Y71" s="4"/>
-    </row>
-    <row r="72" spans="1:25">
+      <c r="Z71" s="4"/>
+      <c r="AA71" s="4"/>
+    </row>
+    <row r="72" spans="1:27">
       <c r="A72" s="4"/>
       <c r="B72" s="4"/>
       <c r="C72" s="4"/>
@@ -6169,8 +6347,8 @@
       <c r="G72" s="4"/>
       <c r="H72" s="4"/>
       <c r="I72" s="4"/>
-      <c r="Q72" s="4"/>
-      <c r="R72" s="4"/>
+      <c r="J72" s="4"/>
+      <c r="K72" s="4"/>
       <c r="S72" s="4"/>
       <c r="T72" s="4"/>
       <c r="U72" s="4"/>
@@ -6178,8 +6356,10 @@
       <c r="W72" s="4"/>
       <c r="X72" s="4"/>
       <c r="Y72" s="4"/>
-    </row>
-    <row r="73" spans="1:25">
+      <c r="Z72" s="4"/>
+      <c r="AA72" s="4"/>
+    </row>
+    <row r="73" spans="1:27">
       <c r="A73" s="4"/>
       <c r="B73" s="4"/>
       <c r="C73" s="4"/>
@@ -6189,8 +6369,8 @@
       <c r="G73" s="4"/>
       <c r="H73" s="4"/>
       <c r="I73" s="4"/>
-      <c r="Q73" s="4"/>
-      <c r="R73" s="4"/>
+      <c r="J73" s="4"/>
+      <c r="K73" s="4"/>
       <c r="S73" s="4"/>
       <c r="T73" s="4"/>
       <c r="U73" s="4"/>
@@ -6198,8 +6378,10 @@
       <c r="W73" s="4"/>
       <c r="X73" s="4"/>
       <c r="Y73" s="4"/>
-    </row>
-    <row r="74" spans="1:25">
+      <c r="Z73" s="4"/>
+      <c r="AA73" s="4"/>
+    </row>
+    <row r="74" spans="1:27">
       <c r="A74" s="4"/>
       <c r="B74" s="4"/>
       <c r="C74" s="4"/>
@@ -6209,8 +6391,8 @@
       <c r="G74" s="4"/>
       <c r="H74" s="4"/>
       <c r="I74" s="4"/>
-      <c r="Q74" s="4"/>
-      <c r="R74" s="4"/>
+      <c r="J74" s="4"/>
+      <c r="K74" s="4"/>
       <c r="S74" s="4"/>
       <c r="T74" s="4"/>
       <c r="U74" s="4"/>
@@ -6218,8 +6400,10 @@
       <c r="W74" s="4"/>
       <c r="X74" s="4"/>
       <c r="Y74" s="4"/>
-    </row>
-    <row r="75" spans="1:25">
+      <c r="Z74" s="4"/>
+      <c r="AA74" s="4"/>
+    </row>
+    <row r="75" spans="1:27">
       <c r="A75" s="4"/>
       <c r="B75" s="4"/>
       <c r="C75" s="4"/>
@@ -6229,8 +6413,8 @@
       <c r="G75" s="4"/>
       <c r="H75" s="4"/>
       <c r="I75" s="4"/>
-      <c r="Q75" s="4"/>
-      <c r="R75" s="4"/>
+      <c r="J75" s="4"/>
+      <c r="K75" s="4"/>
       <c r="S75" s="4"/>
       <c r="T75" s="4"/>
       <c r="U75" s="4"/>
@@ -6238,8 +6422,10 @@
       <c r="W75" s="4"/>
       <c r="X75" s="4"/>
       <c r="Y75" s="4"/>
-    </row>
-    <row r="76" spans="1:25">
+      <c r="Z75" s="4"/>
+      <c r="AA75" s="4"/>
+    </row>
+    <row r="76" spans="1:27">
       <c r="A76" s="4"/>
       <c r="B76" s="4"/>
       <c r="C76" s="4"/>
@@ -6249,8 +6435,8 @@
       <c r="G76" s="4"/>
       <c r="H76" s="4"/>
       <c r="I76" s="4"/>
-      <c r="Q76" s="4"/>
-      <c r="R76" s="4"/>
+      <c r="J76" s="4"/>
+      <c r="K76" s="4"/>
       <c r="S76" s="4"/>
       <c r="T76" s="4"/>
       <c r="U76" s="4"/>
@@ -6258,8 +6444,10 @@
       <c r="W76" s="4"/>
       <c r="X76" s="4"/>
       <c r="Y76" s="4"/>
-    </row>
-    <row r="77" spans="1:25">
+      <c r="Z76" s="4"/>
+      <c r="AA76" s="4"/>
+    </row>
+    <row r="77" spans="1:27">
       <c r="A77" s="4"/>
       <c r="B77" s="4"/>
       <c r="C77" s="4"/>
@@ -6269,8 +6457,8 @@
       <c r="G77" s="4"/>
       <c r="H77" s="4"/>
       <c r="I77" s="4"/>
-      <c r="Q77" s="4"/>
-      <c r="R77" s="4"/>
+      <c r="J77" s="4"/>
+      <c r="K77" s="4"/>
       <c r="S77" s="4"/>
       <c r="T77" s="4"/>
       <c r="U77" s="4"/>
@@ -6278,8 +6466,10 @@
       <c r="W77" s="4"/>
       <c r="X77" s="4"/>
       <c r="Y77" s="4"/>
-    </row>
-    <row r="78" spans="1:25">
+      <c r="Z77" s="4"/>
+      <c r="AA77" s="4"/>
+    </row>
+    <row r="78" spans="1:27">
       <c r="A78" s="4"/>
       <c r="B78" s="4"/>
       <c r="C78" s="4"/>
@@ -6289,8 +6479,8 @@
       <c r="G78" s="4"/>
       <c r="H78" s="4"/>
       <c r="I78" s="4"/>
-      <c r="Q78" s="4"/>
-      <c r="R78" s="4"/>
+      <c r="J78" s="4"/>
+      <c r="K78" s="4"/>
       <c r="S78" s="4"/>
       <c r="T78" s="4"/>
       <c r="U78" s="4"/>
@@ -6298,8 +6488,10 @@
       <c r="W78" s="4"/>
       <c r="X78" s="4"/>
       <c r="Y78" s="4"/>
-    </row>
-    <row r="79" spans="1:25">
+      <c r="Z78" s="4"/>
+      <c r="AA78" s="4"/>
+    </row>
+    <row r="79" spans="1:27">
       <c r="A79" s="4"/>
       <c r="B79" s="4"/>
       <c r="C79" s="4"/>
@@ -6309,8 +6501,8 @@
       <c r="G79" s="4"/>
       <c r="H79" s="4"/>
       <c r="I79" s="4"/>
-      <c r="Q79" s="4"/>
-      <c r="R79" s="4"/>
+      <c r="J79" s="4"/>
+      <c r="K79" s="4"/>
       <c r="S79" s="4"/>
       <c r="T79" s="4"/>
       <c r="U79" s="4"/>
@@ -6318,8 +6510,10 @@
       <c r="W79" s="4"/>
       <c r="X79" s="4"/>
       <c r="Y79" s="4"/>
-    </row>
-    <row r="80" spans="1:25">
+      <c r="Z79" s="4"/>
+      <c r="AA79" s="4"/>
+    </row>
+    <row r="80" spans="1:27">
       <c r="A80" s="4"/>
       <c r="B80" s="4"/>
       <c r="C80" s="4"/>
@@ -6329,8 +6523,8 @@
       <c r="G80" s="4"/>
       <c r="H80" s="4"/>
       <c r="I80" s="4"/>
-      <c r="Q80" s="4"/>
-      <c r="R80" s="4"/>
+      <c r="J80" s="4"/>
+      <c r="K80" s="4"/>
       <c r="S80" s="4"/>
       <c r="T80" s="4"/>
       <c r="U80" s="4"/>
@@ -6338,8 +6532,10 @@
       <c r="W80" s="4"/>
       <c r="X80" s="4"/>
       <c r="Y80" s="4"/>
-    </row>
-    <row r="81" spans="1:25">
+      <c r="Z80" s="4"/>
+      <c r="AA80" s="4"/>
+    </row>
+    <row r="81" spans="1:27">
       <c r="A81" s="4"/>
       <c r="B81" s="4"/>
       <c r="C81" s="4"/>
@@ -6349,8 +6545,8 @@
       <c r="G81" s="4"/>
       <c r="H81" s="4"/>
       <c r="I81" s="4"/>
-      <c r="Q81" s="4"/>
-      <c r="R81" s="4"/>
+      <c r="J81" s="4"/>
+      <c r="K81" s="4"/>
       <c r="S81" s="4"/>
       <c r="T81" s="4"/>
       <c r="U81" s="4"/>
@@ -6358,8 +6554,10 @@
       <c r="W81" s="4"/>
       <c r="X81" s="4"/>
       <c r="Y81" s="4"/>
-    </row>
-    <row r="82" spans="1:25">
+      <c r="Z81" s="4"/>
+      <c r="AA81" s="4"/>
+    </row>
+    <row r="82" spans="1:27">
       <c r="A82" s="4"/>
       <c r="B82" s="4"/>
       <c r="C82" s="4"/>
@@ -6369,8 +6567,8 @@
       <c r="G82" s="4"/>
       <c r="H82" s="4"/>
       <c r="I82" s="4"/>
-      <c r="Q82" s="4"/>
-      <c r="R82" s="4"/>
+      <c r="J82" s="4"/>
+      <c r="K82" s="4"/>
       <c r="S82" s="4"/>
       <c r="T82" s="4"/>
       <c r="U82" s="4"/>
@@ -6378,8 +6576,10 @@
       <c r="W82" s="4"/>
       <c r="X82" s="4"/>
       <c r="Y82" s="4"/>
-    </row>
-    <row r="83" spans="1:25">
+      <c r="Z82" s="4"/>
+      <c r="AA82" s="4"/>
+    </row>
+    <row r="83" spans="1:27">
       <c r="A83" s="4"/>
       <c r="B83" s="4"/>
       <c r="C83" s="4"/>
@@ -6389,8 +6589,8 @@
       <c r="G83" s="4"/>
       <c r="H83" s="4"/>
       <c r="I83" s="4"/>
-      <c r="Q83" s="4"/>
-      <c r="R83" s="4"/>
+      <c r="J83" s="4"/>
+      <c r="K83" s="4"/>
       <c r="S83" s="4"/>
       <c r="T83" s="4"/>
       <c r="U83" s="4"/>
@@ -6398,8 +6598,10 @@
       <c r="W83" s="4"/>
       <c r="X83" s="4"/>
       <c r="Y83" s="4"/>
-    </row>
-    <row r="84" spans="1:25">
+      <c r="Z83" s="4"/>
+      <c r="AA83" s="4"/>
+    </row>
+    <row r="84" spans="1:27">
       <c r="A84" s="4"/>
       <c r="B84" s="4"/>
       <c r="C84" s="4"/>
@@ -6409,8 +6611,8 @@
       <c r="G84" s="4"/>
       <c r="H84" s="4"/>
       <c r="I84" s="4"/>
-      <c r="Q84" s="4"/>
-      <c r="R84" s="4"/>
+      <c r="J84" s="4"/>
+      <c r="K84" s="4"/>
       <c r="S84" s="4"/>
       <c r="T84" s="4"/>
       <c r="U84" s="4"/>
@@ -6418,8 +6620,10 @@
       <c r="W84" s="4"/>
       <c r="X84" s="4"/>
       <c r="Y84" s="4"/>
-    </row>
-    <row r="85" spans="1:25">
+      <c r="Z84" s="4"/>
+      <c r="AA84" s="4"/>
+    </row>
+    <row r="85" spans="1:27">
       <c r="A85" s="4"/>
       <c r="B85" s="4"/>
       <c r="C85" s="4"/>
@@ -6429,8 +6633,8 @@
       <c r="G85" s="4"/>
       <c r="H85" s="4"/>
       <c r="I85" s="4"/>
-      <c r="Q85" s="4"/>
-      <c r="R85" s="4"/>
+      <c r="J85" s="4"/>
+      <c r="K85" s="4"/>
       <c r="S85" s="4"/>
       <c r="T85" s="4"/>
       <c r="U85" s="4"/>
@@ -6438,8 +6642,10 @@
       <c r="W85" s="4"/>
       <c r="X85" s="4"/>
       <c r="Y85" s="4"/>
-    </row>
-    <row r="86" spans="1:25">
+      <c r="Z85" s="4"/>
+      <c r="AA85" s="4"/>
+    </row>
+    <row r="86" spans="1:27">
       <c r="A86" s="4"/>
       <c r="B86" s="4"/>
       <c r="C86" s="4"/>
@@ -6449,8 +6655,8 @@
       <c r="G86" s="4"/>
       <c r="H86" s="4"/>
       <c r="I86" s="4"/>
-      <c r="Q86" s="4"/>
-      <c r="R86" s="4"/>
+      <c r="J86" s="4"/>
+      <c r="K86" s="4"/>
       <c r="S86" s="4"/>
       <c r="T86" s="4"/>
       <c r="U86" s="4"/>
@@ -6458,8 +6664,10 @@
       <c r="W86" s="4"/>
       <c r="X86" s="4"/>
       <c r="Y86" s="4"/>
-    </row>
-    <row r="87" spans="1:25">
+      <c r="Z86" s="4"/>
+      <c r="AA86" s="4"/>
+    </row>
+    <row r="87" spans="1:27">
       <c r="A87" s="4"/>
       <c r="B87" s="4"/>
       <c r="C87" s="4"/>
@@ -6469,8 +6677,8 @@
       <c r="G87" s="4"/>
       <c r="H87" s="4"/>
       <c r="I87" s="4"/>
-      <c r="Q87" s="4"/>
-      <c r="R87" s="4"/>
+      <c r="J87" s="4"/>
+      <c r="K87" s="4"/>
       <c r="S87" s="4"/>
       <c r="T87" s="4"/>
       <c r="U87" s="4"/>
@@ -6478,8 +6686,10 @@
       <c r="W87" s="4"/>
       <c r="X87" s="4"/>
       <c r="Y87" s="4"/>
-    </row>
-    <row r="88" spans="1:25">
+      <c r="Z87" s="4"/>
+      <c r="AA87" s="4"/>
+    </row>
+    <row r="88" spans="1:27">
       <c r="A88" s="4"/>
       <c r="B88" s="4"/>
       <c r="C88" s="4"/>
@@ -6489,8 +6699,8 @@
       <c r="G88" s="4"/>
       <c r="H88" s="4"/>
       <c r="I88" s="4"/>
-      <c r="Q88" s="4"/>
-      <c r="R88" s="4"/>
+      <c r="J88" s="4"/>
+      <c r="K88" s="4"/>
       <c r="S88" s="4"/>
       <c r="T88" s="4"/>
       <c r="U88" s="4"/>
@@ -6498,8 +6708,10 @@
       <c r="W88" s="4"/>
       <c r="X88" s="4"/>
       <c r="Y88" s="4"/>
-    </row>
-    <row r="89" spans="1:25">
+      <c r="Z88" s="4"/>
+      <c r="AA88" s="4"/>
+    </row>
+    <row r="89" spans="1:27">
       <c r="A89" s="4"/>
       <c r="B89" s="4"/>
       <c r="C89" s="4"/>
@@ -6509,8 +6721,8 @@
       <c r="G89" s="4"/>
       <c r="H89" s="4"/>
       <c r="I89" s="4"/>
-      <c r="Q89" s="4"/>
-      <c r="R89" s="4"/>
+      <c r="J89" s="4"/>
+      <c r="K89" s="4"/>
       <c r="S89" s="4"/>
       <c r="T89" s="4"/>
       <c r="U89" s="4"/>
@@ -6518,8 +6730,10 @@
       <c r="W89" s="4"/>
       <c r="X89" s="4"/>
       <c r="Y89" s="4"/>
-    </row>
-    <row r="90" spans="1:25">
+      <c r="Z89" s="4"/>
+      <c r="AA89" s="4"/>
+    </row>
+    <row r="90" spans="1:27">
       <c r="A90" s="4"/>
       <c r="B90" s="4"/>
       <c r="C90" s="4"/>
@@ -6529,8 +6743,8 @@
       <c r="G90" s="4"/>
       <c r="H90" s="4"/>
       <c r="I90" s="4"/>
-      <c r="Q90" s="4"/>
-      <c r="R90" s="4"/>
+      <c r="J90" s="4"/>
+      <c r="K90" s="4"/>
       <c r="S90" s="4"/>
       <c r="T90" s="4"/>
       <c r="U90" s="4"/>
@@ -6538,8 +6752,10 @@
       <c r="W90" s="4"/>
       <c r="X90" s="4"/>
       <c r="Y90" s="4"/>
-    </row>
-    <row r="91" spans="1:25">
+      <c r="Z90" s="4"/>
+      <c r="AA90" s="4"/>
+    </row>
+    <row r="91" spans="1:27">
       <c r="A91" s="4"/>
       <c r="B91" s="4"/>
       <c r="C91" s="4"/>
@@ -6549,8 +6765,8 @@
       <c r="G91" s="4"/>
       <c r="H91" s="4"/>
       <c r="I91" s="4"/>
-      <c r="Q91" s="4"/>
-      <c r="R91" s="4"/>
+      <c r="J91" s="4"/>
+      <c r="K91" s="4"/>
       <c r="S91" s="4"/>
       <c r="T91" s="4"/>
       <c r="U91" s="4"/>
@@ -6558,8 +6774,10 @@
       <c r="W91" s="4"/>
       <c r="X91" s="4"/>
       <c r="Y91" s="4"/>
-    </row>
-    <row r="92" spans="1:25">
+      <c r="Z91" s="4"/>
+      <c r="AA91" s="4"/>
+    </row>
+    <row r="92" spans="1:27">
       <c r="A92" s="4"/>
       <c r="B92" s="4"/>
       <c r="C92" s="4"/>
@@ -6569,8 +6787,8 @@
       <c r="G92" s="4"/>
       <c r="H92" s="4"/>
       <c r="I92" s="4"/>
-      <c r="Q92" s="4"/>
-      <c r="R92" s="4"/>
+      <c r="J92" s="4"/>
+      <c r="K92" s="4"/>
       <c r="S92" s="4"/>
       <c r="T92" s="4"/>
       <c r="U92" s="4"/>
@@ -6578,8 +6796,10 @@
       <c r="W92" s="4"/>
       <c r="X92" s="4"/>
       <c r="Y92" s="4"/>
-    </row>
-    <row r="93" spans="1:25">
+      <c r="Z92" s="4"/>
+      <c r="AA92" s="4"/>
+    </row>
+    <row r="93" spans="1:27">
       <c r="A93" s="4"/>
       <c r="B93" s="4"/>
       <c r="C93" s="4"/>
@@ -6589,8 +6809,8 @@
       <c r="G93" s="4"/>
       <c r="H93" s="4"/>
       <c r="I93" s="4"/>
-      <c r="Q93" s="4"/>
-      <c r="R93" s="4"/>
+      <c r="J93" s="4"/>
+      <c r="K93" s="4"/>
       <c r="S93" s="4"/>
       <c r="T93" s="4"/>
       <c r="U93" s="4"/>
@@ -6598,8 +6818,10 @@
       <c r="W93" s="4"/>
       <c r="X93" s="4"/>
       <c r="Y93" s="4"/>
-    </row>
-    <row r="94" spans="1:25">
+      <c r="Z93" s="4"/>
+      <c r="AA93" s="4"/>
+    </row>
+    <row r="94" spans="1:27">
       <c r="A94" s="4"/>
       <c r="B94" s="4"/>
       <c r="C94" s="4"/>
@@ -6609,8 +6831,8 @@
       <c r="G94" s="4"/>
       <c r="H94" s="4"/>
       <c r="I94" s="4"/>
-      <c r="Q94" s="4"/>
-      <c r="R94" s="4"/>
+      <c r="J94" s="4"/>
+      <c r="K94" s="4"/>
       <c r="S94" s="4"/>
       <c r="T94" s="4"/>
       <c r="U94" s="4"/>
@@ -6618,8 +6840,10 @@
       <c r="W94" s="4"/>
       <c r="X94" s="4"/>
       <c r="Y94" s="4"/>
-    </row>
-    <row r="95" spans="1:25">
+      <c r="Z94" s="4"/>
+      <c r="AA94" s="4"/>
+    </row>
+    <row r="95" spans="1:27">
       <c r="A95" s="4"/>
       <c r="B95" s="4"/>
       <c r="C95" s="4"/>
@@ -6629,8 +6853,8 @@
       <c r="G95" s="4"/>
       <c r="H95" s="4"/>
       <c r="I95" s="4"/>
-      <c r="Q95" s="4"/>
-      <c r="R95" s="4"/>
+      <c r="J95" s="4"/>
+      <c r="K95" s="4"/>
       <c r="S95" s="4"/>
       <c r="T95" s="4"/>
       <c r="U95" s="4"/>
@@ -6638,8 +6862,10 @@
       <c r="W95" s="4"/>
       <c r="X95" s="4"/>
       <c r="Y95" s="4"/>
-    </row>
-    <row r="96" spans="1:25">
+      <c r="Z95" s="4"/>
+      <c r="AA95" s="4"/>
+    </row>
+    <row r="96" spans="1:27">
       <c r="A96" s="4"/>
       <c r="B96" s="4"/>
       <c r="C96" s="4"/>
@@ -6649,8 +6875,8 @@
       <c r="G96" s="4"/>
       <c r="H96" s="4"/>
       <c r="I96" s="4"/>
-      <c r="Q96" s="4"/>
-      <c r="R96" s="4"/>
+      <c r="J96" s="4"/>
+      <c r="K96" s="4"/>
       <c r="S96" s="4"/>
       <c r="T96" s="4"/>
       <c r="U96" s="4"/>
@@ -6658,8 +6884,10 @@
       <c r="W96" s="4"/>
       <c r="X96" s="4"/>
       <c r="Y96" s="4"/>
-    </row>
-    <row r="97" spans="1:25">
+      <c r="Z96" s="4"/>
+      <c r="AA96" s="4"/>
+    </row>
+    <row r="97" spans="1:27">
       <c r="A97" s="4"/>
       <c r="B97" s="4"/>
       <c r="C97" s="4"/>
@@ -6669,8 +6897,8 @@
       <c r="G97" s="4"/>
       <c r="H97" s="4"/>
       <c r="I97" s="4"/>
-      <c r="Q97" s="4"/>
-      <c r="R97" s="4"/>
+      <c r="J97" s="4"/>
+      <c r="K97" s="4"/>
       <c r="S97" s="4"/>
       <c r="T97" s="4"/>
       <c r="U97" s="4"/>
@@ -6678,8 +6906,10 @@
       <c r="W97" s="4"/>
       <c r="X97" s="4"/>
       <c r="Y97" s="4"/>
-    </row>
-    <row r="98" spans="1:25">
+      <c r="Z97" s="4"/>
+      <c r="AA97" s="4"/>
+    </row>
+    <row r="98" spans="1:27">
       <c r="A98" s="4"/>
       <c r="B98" s="4"/>
       <c r="C98" s="4"/>
@@ -6689,8 +6919,8 @@
       <c r="G98" s="4"/>
       <c r="H98" s="4"/>
       <c r="I98" s="4"/>
-      <c r="Q98" s="4"/>
-      <c r="R98" s="4"/>
+      <c r="J98" s="4"/>
+      <c r="K98" s="4"/>
       <c r="S98" s="4"/>
       <c r="T98" s="4"/>
       <c r="U98" s="4"/>
@@ -6698,8 +6928,10 @@
       <c r="W98" s="4"/>
       <c r="X98" s="4"/>
       <c r="Y98" s="4"/>
-    </row>
-    <row r="99" spans="1:25">
+      <c r="Z98" s="4"/>
+      <c r="AA98" s="4"/>
+    </row>
+    <row r="99" spans="1:27">
       <c r="A99" s="4"/>
       <c r="B99" s="4"/>
       <c r="C99" s="4"/>
@@ -6709,8 +6941,8 @@
       <c r="G99" s="4"/>
       <c r="H99" s="4"/>
       <c r="I99" s="4"/>
-      <c r="Q99" s="4"/>
-      <c r="R99" s="4"/>
+      <c r="J99" s="4"/>
+      <c r="K99" s="4"/>
       <c r="S99" s="4"/>
       <c r="T99" s="4"/>
       <c r="U99" s="4"/>
@@ -6718,8 +6950,10 @@
       <c r="W99" s="4"/>
       <c r="X99" s="4"/>
       <c r="Y99" s="4"/>
-    </row>
-    <row r="100" spans="1:25">
+      <c r="Z99" s="4"/>
+      <c r="AA99" s="4"/>
+    </row>
+    <row r="100" spans="1:27">
       <c r="A100" s="4"/>
       <c r="B100" s="4"/>
       <c r="C100" s="4"/>
@@ -6729,8 +6963,8 @@
       <c r="G100" s="4"/>
       <c r="H100" s="4"/>
       <c r="I100" s="4"/>
-      <c r="Q100" s="4"/>
-      <c r="R100" s="4"/>
+      <c r="J100" s="4"/>
+      <c r="K100" s="4"/>
       <c r="S100" s="4"/>
       <c r="T100" s="4"/>
       <c r="U100" s="4"/>
@@ -6738,8 +6972,10 @@
       <c r="W100" s="4"/>
       <c r="X100" s="4"/>
       <c r="Y100" s="4"/>
-    </row>
-    <row r="101" spans="1:25">
+      <c r="Z100" s="4"/>
+      <c r="AA100" s="4"/>
+    </row>
+    <row r="101" spans="1:27">
       <c r="A101" s="4"/>
       <c r="B101" s="4"/>
       <c r="C101" s="4"/>
@@ -6749,8 +6985,8 @@
       <c r="G101" s="4"/>
       <c r="H101" s="4"/>
       <c r="I101" s="4"/>
-      <c r="Q101" s="4"/>
-      <c r="R101" s="4"/>
+      <c r="J101" s="4"/>
+      <c r="K101" s="4"/>
       <c r="S101" s="4"/>
       <c r="T101" s="4"/>
       <c r="U101" s="4"/>
@@ -6758,8 +6994,10 @@
       <c r="W101" s="4"/>
       <c r="X101" s="4"/>
       <c r="Y101" s="4"/>
-    </row>
-    <row r="102" spans="1:25">
+      <c r="Z101" s="4"/>
+      <c r="AA101" s="4"/>
+    </row>
+    <row r="102" spans="1:27">
       <c r="A102" s="4"/>
       <c r="B102" s="4"/>
       <c r="C102" s="4"/>
@@ -6769,8 +7007,8 @@
       <c r="G102" s="4"/>
       <c r="H102" s="4"/>
       <c r="I102" s="4"/>
-      <c r="Q102" s="4"/>
-      <c r="R102" s="4"/>
+      <c r="J102" s="4"/>
+      <c r="K102" s="4"/>
       <c r="S102" s="4"/>
       <c r="T102" s="4"/>
       <c r="U102" s="4"/>
@@ -6778,8 +7016,10 @@
       <c r="W102" s="4"/>
       <c r="X102" s="4"/>
       <c r="Y102" s="4"/>
-    </row>
-    <row r="103" spans="1:25">
+      <c r="Z102" s="4"/>
+      <c r="AA102" s="4"/>
+    </row>
+    <row r="103" spans="1:27">
       <c r="A103" s="4"/>
       <c r="B103" s="4"/>
       <c r="C103" s="4"/>
@@ -6789,8 +7029,8 @@
       <c r="G103" s="4"/>
       <c r="H103" s="4"/>
       <c r="I103" s="4"/>
-      <c r="Q103" s="4"/>
-      <c r="R103" s="4"/>
+      <c r="J103" s="4"/>
+      <c r="K103" s="4"/>
       <c r="S103" s="4"/>
       <c r="T103" s="4"/>
       <c r="U103" s="4"/>
@@ -6798,8 +7038,10 @@
       <c r="W103" s="4"/>
       <c r="X103" s="4"/>
       <c r="Y103" s="4"/>
-    </row>
-    <row r="104" spans="1:25">
+      <c r="Z103" s="4"/>
+      <c r="AA103" s="4"/>
+    </row>
+    <row r="104" spans="1:27">
       <c r="A104" s="4"/>
       <c r="B104" s="4"/>
       <c r="C104" s="4"/>
@@ -6809,8 +7051,8 @@
       <c r="G104" s="4"/>
       <c r="H104" s="4"/>
       <c r="I104" s="4"/>
-      <c r="Q104" s="4"/>
-      <c r="R104" s="4"/>
+      <c r="J104" s="4"/>
+      <c r="K104" s="4"/>
       <c r="S104" s="4"/>
       <c r="T104" s="4"/>
       <c r="U104" s="4"/>
@@ -6818,8 +7060,10 @@
       <c r="W104" s="4"/>
       <c r="X104" s="4"/>
       <c r="Y104" s="4"/>
-    </row>
-    <row r="105" spans="1:25">
+      <c r="Z104" s="4"/>
+      <c r="AA104" s="4"/>
+    </row>
+    <row r="105" spans="1:27">
       <c r="A105" s="4"/>
       <c r="B105" s="4"/>
       <c r="C105" s="4"/>
@@ -6829,8 +7073,8 @@
       <c r="G105" s="4"/>
       <c r="H105" s="4"/>
       <c r="I105" s="4"/>
-      <c r="Q105" s="4"/>
-      <c r="R105" s="4"/>
+      <c r="J105" s="4"/>
+      <c r="K105" s="4"/>
       <c r="S105" s="4"/>
       <c r="T105" s="4"/>
       <c r="U105" s="4"/>
@@ -6838,8 +7082,10 @@
       <c r="W105" s="4"/>
       <c r="X105" s="4"/>
       <c r="Y105" s="4"/>
-    </row>
-    <row r="106" spans="1:25">
+      <c r="Z105" s="4"/>
+      <c r="AA105" s="4"/>
+    </row>
+    <row r="106" spans="1:27">
       <c r="A106" s="4"/>
       <c r="B106" s="4"/>
       <c r="C106" s="4"/>
@@ -6849,8 +7095,8 @@
       <c r="G106" s="4"/>
       <c r="H106" s="4"/>
       <c r="I106" s="4"/>
-      <c r="Q106" s="4"/>
-      <c r="R106" s="4"/>
+      <c r="J106" s="4"/>
+      <c r="K106" s="4"/>
       <c r="S106" s="4"/>
       <c r="T106" s="4"/>
       <c r="U106" s="4"/>
@@ -6858,8 +7104,10 @@
       <c r="W106" s="4"/>
       <c r="X106" s="4"/>
       <c r="Y106" s="4"/>
-    </row>
-    <row r="107" spans="1:25">
+      <c r="Z106" s="4"/>
+      <c r="AA106" s="4"/>
+    </row>
+    <row r="107" spans="1:27">
       <c r="A107" s="4"/>
       <c r="B107" s="4"/>
       <c r="C107" s="4"/>
@@ -6869,8 +7117,8 @@
       <c r="G107" s="4"/>
       <c r="H107" s="4"/>
       <c r="I107" s="4"/>
-      <c r="Q107" s="4"/>
-      <c r="R107" s="4"/>
+      <c r="J107" s="4"/>
+      <c r="K107" s="4"/>
       <c r="S107" s="4"/>
       <c r="T107" s="4"/>
       <c r="U107" s="4"/>
@@ -6878,8 +7126,10 @@
       <c r="W107" s="4"/>
       <c r="X107" s="4"/>
       <c r="Y107" s="4"/>
-    </row>
-    <row r="108" spans="1:25">
+      <c r="Z107" s="4"/>
+      <c r="AA107" s="4"/>
+    </row>
+    <row r="108" spans="1:27">
       <c r="A108" s="4"/>
       <c r="B108" s="4"/>
       <c r="C108" s="4"/>
@@ -6889,8 +7139,8 @@
       <c r="G108" s="4"/>
       <c r="H108" s="4"/>
       <c r="I108" s="4"/>
-      <c r="Q108" s="4"/>
-      <c r="R108" s="4"/>
+      <c r="J108" s="4"/>
+      <c r="K108" s="4"/>
       <c r="S108" s="4"/>
       <c r="T108" s="4"/>
       <c r="U108" s="4"/>
@@ -6898,8 +7148,10 @@
       <c r="W108" s="4"/>
       <c r="X108" s="4"/>
       <c r="Y108" s="4"/>
-    </row>
-    <row r="109" spans="1:25">
+      <c r="Z108" s="4"/>
+      <c r="AA108" s="4"/>
+    </row>
+    <row r="109" spans="1:27">
       <c r="A109" s="4"/>
       <c r="B109" s="4"/>
       <c r="C109" s="4"/>
@@ -6909,8 +7161,8 @@
       <c r="G109" s="4"/>
       <c r="H109" s="4"/>
       <c r="I109" s="4"/>
-      <c r="Q109" s="4"/>
-      <c r="R109" s="4"/>
+      <c r="J109" s="4"/>
+      <c r="K109" s="4"/>
       <c r="S109" s="4"/>
       <c r="T109" s="4"/>
       <c r="U109" s="4"/>
@@ -6918,8 +7170,10 @@
       <c r="W109" s="4"/>
       <c r="X109" s="4"/>
       <c r="Y109" s="4"/>
-    </row>
-    <row r="110" spans="1:25">
+      <c r="Z109" s="4"/>
+      <c r="AA109" s="4"/>
+    </row>
+    <row r="110" spans="1:27">
       <c r="A110" s="4"/>
       <c r="B110" s="4"/>
       <c r="C110" s="4"/>
@@ -6929,8 +7183,8 @@
       <c r="G110" s="4"/>
       <c r="H110" s="4"/>
       <c r="I110" s="4"/>
-      <c r="Q110" s="4"/>
-      <c r="R110" s="4"/>
+      <c r="J110" s="4"/>
+      <c r="K110" s="4"/>
       <c r="S110" s="4"/>
       <c r="T110" s="4"/>
       <c r="U110" s="4"/>
@@ -6938,8 +7192,10 @@
       <c r="W110" s="4"/>
       <c r="X110" s="4"/>
       <c r="Y110" s="4"/>
-    </row>
-    <row r="111" spans="1:25">
+      <c r="Z110" s="4"/>
+      <c r="AA110" s="4"/>
+    </row>
+    <row r="111" spans="1:27">
       <c r="A111" s="4"/>
       <c r="B111" s="4"/>
       <c r="C111" s="4"/>
@@ -6949,8 +7205,8 @@
       <c r="G111" s="4"/>
       <c r="H111" s="4"/>
       <c r="I111" s="4"/>
-      <c r="Q111" s="4"/>
-      <c r="R111" s="4"/>
+      <c r="J111" s="4"/>
+      <c r="K111" s="4"/>
       <c r="S111" s="4"/>
       <c r="T111" s="4"/>
       <c r="U111" s="4"/>
@@ -6958,8 +7214,10 @@
       <c r="W111" s="4"/>
       <c r="X111" s="4"/>
       <c r="Y111" s="4"/>
-    </row>
-    <row r="112" spans="1:25">
+      <c r="Z111" s="4"/>
+      <c r="AA111" s="4"/>
+    </row>
+    <row r="112" spans="1:27">
       <c r="A112" s="4"/>
       <c r="B112" s="4"/>
       <c r="C112" s="4"/>
@@ -6969,8 +7227,8 @@
       <c r="G112" s="4"/>
       <c r="H112" s="4"/>
       <c r="I112" s="4"/>
-      <c r="Q112" s="4"/>
-      <c r="R112" s="4"/>
+      <c r="J112" s="4"/>
+      <c r="K112" s="4"/>
       <c r="S112" s="4"/>
       <c r="T112" s="4"/>
       <c r="U112" s="4"/>
@@ -6978,8 +7236,10 @@
       <c r="W112" s="4"/>
       <c r="X112" s="4"/>
       <c r="Y112" s="4"/>
-    </row>
-    <row r="113" spans="1:25">
+      <c r="Z112" s="4"/>
+      <c r="AA112" s="4"/>
+    </row>
+    <row r="113" spans="1:27">
       <c r="A113" s="4"/>
       <c r="B113" s="4"/>
       <c r="C113" s="4"/>
@@ -6989,8 +7249,8 @@
       <c r="G113" s="4"/>
       <c r="H113" s="4"/>
       <c r="I113" s="4"/>
-      <c r="Q113" s="4"/>
-      <c r="R113" s="4"/>
+      <c r="J113" s="4"/>
+      <c r="K113" s="4"/>
       <c r="S113" s="4"/>
       <c r="T113" s="4"/>
       <c r="U113" s="4"/>
@@ -6998,8 +7258,10 @@
       <c r="W113" s="4"/>
       <c r="X113" s="4"/>
       <c r="Y113" s="4"/>
-    </row>
-    <row r="114" spans="1:25">
+      <c r="Z113" s="4"/>
+      <c r="AA113" s="4"/>
+    </row>
+    <row r="114" spans="1:27">
       <c r="A114" s="4"/>
       <c r="B114" s="4"/>
       <c r="C114" s="4"/>
@@ -7009,8 +7271,8 @@
       <c r="G114" s="4"/>
       <c r="H114" s="4"/>
       <c r="I114" s="4"/>
-      <c r="Q114" s="4"/>
-      <c r="R114" s="4"/>
+      <c r="J114" s="4"/>
+      <c r="K114" s="4"/>
       <c r="S114" s="4"/>
       <c r="T114" s="4"/>
       <c r="U114" s="4"/>
@@ -7018,8 +7280,10 @@
       <c r="W114" s="4"/>
       <c r="X114" s="4"/>
       <c r="Y114" s="4"/>
-    </row>
-    <row r="115" spans="1:25">
+      <c r="Z114" s="4"/>
+      <c r="AA114" s="4"/>
+    </row>
+    <row r="115" spans="1:27">
       <c r="A115" s="4"/>
       <c r="B115" s="4"/>
       <c r="C115" s="4"/>
@@ -7029,8 +7293,8 @@
       <c r="G115" s="4"/>
       <c r="H115" s="4"/>
       <c r="I115" s="4"/>
-      <c r="Q115" s="4"/>
-      <c r="R115" s="4"/>
+      <c r="J115" s="4"/>
+      <c r="K115" s="4"/>
       <c r="S115" s="4"/>
       <c r="T115" s="4"/>
       <c r="U115" s="4"/>
@@ -7038,8 +7302,10 @@
       <c r="W115" s="4"/>
       <c r="X115" s="4"/>
       <c r="Y115" s="4"/>
-    </row>
-    <row r="116" spans="1:25">
+      <c r="Z115" s="4"/>
+      <c r="AA115" s="4"/>
+    </row>
+    <row r="116" spans="1:27">
       <c r="A116" s="4"/>
       <c r="B116" s="4"/>
       <c r="C116" s="4"/>
@@ -7049,8 +7315,8 @@
       <c r="G116" s="4"/>
       <c r="H116" s="4"/>
       <c r="I116" s="4"/>
-      <c r="Q116" s="4"/>
-      <c r="R116" s="4"/>
+      <c r="J116" s="4"/>
+      <c r="K116" s="4"/>
       <c r="S116" s="4"/>
       <c r="T116" s="4"/>
       <c r="U116" s="4"/>
@@ -7058,8 +7324,10 @@
       <c r="W116" s="4"/>
       <c r="X116" s="4"/>
       <c r="Y116" s="4"/>
-    </row>
-    <row r="117" spans="1:25">
+      <c r="Z116" s="4"/>
+      <c r="AA116" s="4"/>
+    </row>
+    <row r="117" spans="1:27">
       <c r="A117" s="4"/>
       <c r="B117" s="4"/>
       <c r="C117" s="4"/>
@@ -7069,8 +7337,8 @@
       <c r="G117" s="4"/>
       <c r="H117" s="4"/>
       <c r="I117" s="4"/>
-      <c r="Q117" s="4"/>
-      <c r="R117" s="4"/>
+      <c r="J117" s="4"/>
+      <c r="K117" s="4"/>
       <c r="S117" s="4"/>
       <c r="T117" s="4"/>
       <c r="U117" s="4"/>
@@ -7078,8 +7346,10 @@
       <c r="W117" s="4"/>
       <c r="X117" s="4"/>
       <c r="Y117" s="4"/>
-    </row>
-    <row r="118" spans="1:25">
+      <c r="Z117" s="4"/>
+      <c r="AA117" s="4"/>
+    </row>
+    <row r="118" spans="1:27">
       <c r="A118" s="4"/>
       <c r="B118" s="4"/>
       <c r="C118" s="4"/>
@@ -7089,8 +7359,8 @@
       <c r="G118" s="4"/>
       <c r="H118" s="4"/>
       <c r="I118" s="4"/>
-      <c r="Q118" s="4"/>
-      <c r="R118" s="4"/>
+      <c r="J118" s="4"/>
+      <c r="K118" s="4"/>
       <c r="S118" s="4"/>
       <c r="T118" s="4"/>
       <c r="U118" s="4"/>
@@ -7098,8 +7368,10 @@
       <c r="W118" s="4"/>
       <c r="X118" s="4"/>
       <c r="Y118" s="4"/>
-    </row>
-    <row r="119" spans="1:25">
+      <c r="Z118" s="4"/>
+      <c r="AA118" s="4"/>
+    </row>
+    <row r="119" spans="1:27">
       <c r="A119" s="4"/>
       <c r="B119" s="4"/>
       <c r="C119" s="4"/>
@@ -7109,8 +7381,8 @@
       <c r="G119" s="4"/>
       <c r="H119" s="4"/>
       <c r="I119" s="4"/>
-      <c r="Q119" s="4"/>
-      <c r="R119" s="4"/>
+      <c r="J119" s="4"/>
+      <c r="K119" s="4"/>
       <c r="S119" s="4"/>
       <c r="T119" s="4"/>
       <c r="U119" s="4"/>
@@ -7118,8 +7390,10 @@
       <c r="W119" s="4"/>
       <c r="X119" s="4"/>
       <c r="Y119" s="4"/>
-    </row>
-    <row r="120" spans="1:25">
+      <c r="Z119" s="4"/>
+      <c r="AA119" s="4"/>
+    </row>
+    <row r="120" spans="1:27">
       <c r="A120" s="4"/>
       <c r="B120" s="4"/>
       <c r="C120" s="4"/>
@@ -7129,8 +7403,8 @@
       <c r="G120" s="4"/>
       <c r="H120" s="4"/>
       <c r="I120" s="4"/>
-      <c r="Q120" s="4"/>
-      <c r="R120" s="4"/>
+      <c r="J120" s="4"/>
+      <c r="K120" s="4"/>
       <c r="S120" s="4"/>
       <c r="T120" s="4"/>
       <c r="U120" s="4"/>
@@ -7138,8 +7412,10 @@
       <c r="W120" s="4"/>
       <c r="X120" s="4"/>
       <c r="Y120" s="4"/>
-    </row>
-    <row r="121" spans="1:25">
+      <c r="Z120" s="4"/>
+      <c r="AA120" s="4"/>
+    </row>
+    <row r="121" spans="1:27">
       <c r="A121" s="4"/>
       <c r="B121" s="4"/>
       <c r="C121" s="4"/>
@@ -7149,8 +7425,8 @@
       <c r="G121" s="4"/>
       <c r="H121" s="4"/>
       <c r="I121" s="4"/>
-      <c r="Q121" s="4"/>
-      <c r="R121" s="4"/>
+      <c r="J121" s="4"/>
+      <c r="K121" s="4"/>
       <c r="S121" s="4"/>
       <c r="T121" s="4"/>
       <c r="U121" s="4"/>
@@ -7158,8 +7434,10 @@
       <c r="W121" s="4"/>
       <c r="X121" s="4"/>
       <c r="Y121" s="4"/>
-    </row>
-    <row r="122" spans="1:25">
+      <c r="Z121" s="4"/>
+      <c r="AA121" s="4"/>
+    </row>
+    <row r="122" spans="1:27">
       <c r="A122" s="4"/>
       <c r="B122" s="4"/>
       <c r="C122" s="4"/>
@@ -7169,8 +7447,8 @@
       <c r="G122" s="4"/>
       <c r="H122" s="4"/>
       <c r="I122" s="4"/>
-      <c r="Q122" s="4"/>
-      <c r="R122" s="4"/>
+      <c r="J122" s="4"/>
+      <c r="K122" s="4"/>
       <c r="S122" s="4"/>
       <c r="T122" s="4"/>
       <c r="U122" s="4"/>
@@ -7178,8 +7456,10 @@
       <c r="W122" s="4"/>
       <c r="X122" s="4"/>
       <c r="Y122" s="4"/>
-    </row>
-    <row r="123" spans="1:25">
+      <c r="Z122" s="4"/>
+      <c r="AA122" s="4"/>
+    </row>
+    <row r="123" spans="1:27">
       <c r="A123" s="4"/>
       <c r="B123" s="4"/>
       <c r="C123" s="4"/>
@@ -7189,8 +7469,8 @@
       <c r="G123" s="4"/>
       <c r="H123" s="4"/>
       <c r="I123" s="4"/>
-      <c r="Q123" s="4"/>
-      <c r="R123" s="4"/>
+      <c r="J123" s="4"/>
+      <c r="K123" s="4"/>
       <c r="S123" s="4"/>
       <c r="T123" s="4"/>
       <c r="U123" s="4"/>
@@ -7198,8 +7478,10 @@
       <c r="W123" s="4"/>
       <c r="X123" s="4"/>
       <c r="Y123" s="4"/>
-    </row>
-    <row r="124" spans="1:25">
+      <c r="Z123" s="4"/>
+      <c r="AA123" s="4"/>
+    </row>
+    <row r="124" spans="1:27">
       <c r="A124" s="4"/>
       <c r="B124" s="4"/>
       <c r="C124" s="4"/>
@@ -7209,8 +7491,8 @@
       <c r="G124" s="4"/>
       <c r="H124" s="4"/>
       <c r="I124" s="4"/>
-      <c r="Q124" s="4"/>
-      <c r="R124" s="4"/>
+      <c r="J124" s="4"/>
+      <c r="K124" s="4"/>
       <c r="S124" s="4"/>
       <c r="T124" s="4"/>
       <c r="U124" s="4"/>
@@ -7218,8 +7500,10 @@
       <c r="W124" s="4"/>
       <c r="X124" s="4"/>
       <c r="Y124" s="4"/>
-    </row>
-    <row r="125" spans="1:25">
+      <c r="Z124" s="4"/>
+      <c r="AA124" s="4"/>
+    </row>
+    <row r="125" spans="1:27">
       <c r="A125" s="4"/>
       <c r="B125" s="4"/>
       <c r="C125" s="4"/>
@@ -7229,8 +7513,8 @@
       <c r="G125" s="4"/>
       <c r="H125" s="4"/>
       <c r="I125" s="4"/>
-      <c r="Q125" s="4"/>
-      <c r="R125" s="4"/>
+      <c r="J125" s="4"/>
+      <c r="K125" s="4"/>
       <c r="S125" s="4"/>
       <c r="T125" s="4"/>
       <c r="U125" s="4"/>
@@ -7238,8 +7522,10 @@
       <c r="W125" s="4"/>
       <c r="X125" s="4"/>
       <c r="Y125" s="4"/>
-    </row>
-    <row r="126" spans="1:25">
+      <c r="Z125" s="4"/>
+      <c r="AA125" s="4"/>
+    </row>
+    <row r="126" spans="1:27">
       <c r="A126" s="4"/>
       <c r="B126" s="4"/>
       <c r="C126" s="4"/>
@@ -7249,8 +7535,8 @@
       <c r="G126" s="4"/>
       <c r="H126" s="4"/>
       <c r="I126" s="4"/>
-      <c r="Q126" s="4"/>
-      <c r="R126" s="4"/>
+      <c r="J126" s="4"/>
+      <c r="K126" s="4"/>
       <c r="S126" s="4"/>
       <c r="T126" s="4"/>
       <c r="U126" s="4"/>
@@ -7258,8 +7544,10 @@
       <c r="W126" s="4"/>
       <c r="X126" s="4"/>
       <c r="Y126" s="4"/>
-    </row>
-    <row r="127" spans="1:25">
+      <c r="Z126" s="4"/>
+      <c r="AA126" s="4"/>
+    </row>
+    <row r="127" spans="1:27">
       <c r="A127" s="4"/>
       <c r="B127" s="4"/>
       <c r="C127" s="4"/>
@@ -7269,8 +7557,8 @@
       <c r="G127" s="4"/>
       <c r="H127" s="4"/>
       <c r="I127" s="4"/>
-      <c r="Q127" s="4"/>
-      <c r="R127" s="4"/>
+      <c r="J127" s="4"/>
+      <c r="K127" s="4"/>
       <c r="S127" s="4"/>
       <c r="T127" s="4"/>
       <c r="U127" s="4"/>
@@ -7278,8 +7566,10 @@
       <c r="W127" s="4"/>
       <c r="X127" s="4"/>
       <c r="Y127" s="4"/>
-    </row>
-    <row r="128" spans="1:25">
+      <c r="Z127" s="4"/>
+      <c r="AA127" s="4"/>
+    </row>
+    <row r="128" spans="1:27">
       <c r="A128" s="4"/>
       <c r="B128" s="4"/>
       <c r="C128" s="4"/>
@@ -7289,8 +7579,8 @@
       <c r="G128" s="4"/>
       <c r="H128" s="4"/>
       <c r="I128" s="4"/>
-      <c r="Q128" s="4"/>
-      <c r="R128" s="4"/>
+      <c r="J128" s="4"/>
+      <c r="K128" s="4"/>
       <c r="S128" s="4"/>
       <c r="T128" s="4"/>
       <c r="U128" s="4"/>
@@ -7298,8 +7588,10 @@
       <c r="W128" s="4"/>
       <c r="X128" s="4"/>
       <c r="Y128" s="4"/>
-    </row>
-    <row r="129" spans="1:25">
+      <c r="Z128" s="4"/>
+      <c r="AA128" s="4"/>
+    </row>
+    <row r="129" spans="1:27">
       <c r="A129" s="4"/>
       <c r="B129" s="4"/>
       <c r="C129" s="4"/>
@@ -7309,8 +7601,8 @@
       <c r="G129" s="4"/>
       <c r="H129" s="4"/>
       <c r="I129" s="4"/>
-      <c r="Q129" s="4"/>
-      <c r="R129" s="4"/>
+      <c r="J129" s="4"/>
+      <c r="K129" s="4"/>
       <c r="S129" s="4"/>
       <c r="T129" s="4"/>
       <c r="U129" s="4"/>
@@ -7318,8 +7610,10 @@
       <c r="W129" s="4"/>
       <c r="X129" s="4"/>
       <c r="Y129" s="4"/>
-    </row>
-    <row r="130" spans="1:25">
+      <c r="Z129" s="4"/>
+      <c r="AA129" s="4"/>
+    </row>
+    <row r="130" spans="1:27">
       <c r="A130" s="4"/>
       <c r="B130" s="4"/>
       <c r="C130" s="4"/>
@@ -7329,8 +7623,8 @@
       <c r="G130" s="4"/>
       <c r="H130" s="4"/>
       <c r="I130" s="4"/>
-      <c r="Q130" s="4"/>
-      <c r="R130" s="4"/>
+      <c r="J130" s="4"/>
+      <c r="K130" s="4"/>
       <c r="S130" s="4"/>
       <c r="T130" s="4"/>
       <c r="U130" s="4"/>
@@ -7338,8 +7632,10 @@
       <c r="W130" s="4"/>
       <c r="X130" s="4"/>
       <c r="Y130" s="4"/>
-    </row>
-    <row r="131" spans="1:25">
+      <c r="Z130" s="4"/>
+      <c r="AA130" s="4"/>
+    </row>
+    <row r="131" spans="1:27">
       <c r="A131" s="4"/>
       <c r="B131" s="4"/>
       <c r="C131" s="4"/>
@@ -7349,8 +7645,8 @@
       <c r="G131" s="4"/>
       <c r="H131" s="4"/>
       <c r="I131" s="4"/>
-      <c r="Q131" s="4"/>
-      <c r="R131" s="4"/>
+      <c r="J131" s="4"/>
+      <c r="K131" s="4"/>
       <c r="S131" s="4"/>
       <c r="T131" s="4"/>
       <c r="U131" s="4"/>
@@ -7358,8 +7654,10 @@
       <c r="W131" s="4"/>
       <c r="X131" s="4"/>
       <c r="Y131" s="4"/>
-    </row>
-    <row r="132" spans="1:25">
+      <c r="Z131" s="4"/>
+      <c r="AA131" s="4"/>
+    </row>
+    <row r="132" spans="1:27">
       <c r="A132" s="4"/>
       <c r="B132" s="4"/>
       <c r="C132" s="4"/>
@@ -7369,8 +7667,8 @@
       <c r="G132" s="4"/>
       <c r="H132" s="4"/>
       <c r="I132" s="4"/>
-      <c r="Q132" s="4"/>
-      <c r="R132" s="4"/>
+      <c r="J132" s="4"/>
+      <c r="K132" s="4"/>
       <c r="S132" s="4"/>
       <c r="T132" s="4"/>
       <c r="U132" s="4"/>
@@ -7378,8 +7676,10 @@
       <c r="W132" s="4"/>
       <c r="X132" s="4"/>
       <c r="Y132" s="4"/>
-    </row>
-    <row r="133" spans="1:25">
+      <c r="Z132" s="4"/>
+      <c r="AA132" s="4"/>
+    </row>
+    <row r="133" spans="1:27">
       <c r="A133" s="4"/>
       <c r="B133" s="4"/>
       <c r="C133" s="4"/>
@@ -7389,8 +7689,8 @@
       <c r="G133" s="4"/>
       <c r="H133" s="4"/>
       <c r="I133" s="4"/>
-      <c r="Q133" s="4"/>
-      <c r="R133" s="4"/>
+      <c r="J133" s="4"/>
+      <c r="K133" s="4"/>
       <c r="S133" s="4"/>
       <c r="T133" s="4"/>
       <c r="U133" s="4"/>
@@ -7398,8 +7698,10 @@
       <c r="W133" s="4"/>
       <c r="X133" s="4"/>
       <c r="Y133" s="4"/>
-    </row>
-    <row r="134" spans="1:25">
+      <c r="Z133" s="4"/>
+      <c r="AA133" s="4"/>
+    </row>
+    <row r="134" spans="1:27">
       <c r="A134" s="4"/>
       <c r="B134" s="4"/>
       <c r="C134" s="4"/>
@@ -7409,8 +7711,8 @@
       <c r="G134" s="4"/>
       <c r="H134" s="4"/>
       <c r="I134" s="4"/>
-      <c r="Q134" s="4"/>
-      <c r="R134" s="4"/>
+      <c r="J134" s="4"/>
+      <c r="K134" s="4"/>
       <c r="S134" s="4"/>
       <c r="T134" s="4"/>
       <c r="U134" s="4"/>
@@ -7418,8 +7720,10 @@
       <c r="W134" s="4"/>
       <c r="X134" s="4"/>
       <c r="Y134" s="4"/>
-    </row>
-    <row r="135" spans="1:25">
+      <c r="Z134" s="4"/>
+      <c r="AA134" s="4"/>
+    </row>
+    <row r="135" spans="1:27">
       <c r="A135" s="4"/>
       <c r="B135" s="4"/>
       <c r="C135" s="4"/>
@@ -7429,8 +7733,8 @@
       <c r="G135" s="4"/>
       <c r="H135" s="4"/>
       <c r="I135" s="4"/>
-      <c r="Q135" s="4"/>
-      <c r="R135" s="4"/>
+      <c r="J135" s="4"/>
+      <c r="K135" s="4"/>
       <c r="S135" s="4"/>
       <c r="T135" s="4"/>
       <c r="U135" s="4"/>
@@ -7438,8 +7742,10 @@
       <c r="W135" s="4"/>
       <c r="X135" s="4"/>
       <c r="Y135" s="4"/>
-    </row>
-    <row r="136" spans="1:25">
+      <c r="Z135" s="4"/>
+      <c r="AA135" s="4"/>
+    </row>
+    <row r="136" spans="1:27">
       <c r="A136" s="4"/>
       <c r="B136" s="4"/>
       <c r="C136" s="4"/>
@@ -7449,8 +7755,8 @@
       <c r="G136" s="4"/>
       <c r="H136" s="4"/>
       <c r="I136" s="4"/>
-      <c r="Q136" s="4"/>
-      <c r="R136" s="4"/>
+      <c r="J136" s="4"/>
+      <c r="K136" s="4"/>
       <c r="S136" s="4"/>
       <c r="T136" s="4"/>
       <c r="U136" s="4"/>
@@ -7458,8 +7764,10 @@
       <c r="W136" s="4"/>
       <c r="X136" s="4"/>
       <c r="Y136" s="4"/>
-    </row>
-    <row r="137" spans="1:25">
+      <c r="Z136" s="4"/>
+      <c r="AA136" s="4"/>
+    </row>
+    <row r="137" spans="1:27">
       <c r="A137" s="4"/>
       <c r="B137" s="4"/>
       <c r="C137" s="4"/>
@@ -7469,8 +7777,8 @@
       <c r="G137" s="4"/>
       <c r="H137" s="4"/>
       <c r="I137" s="4"/>
-      <c r="Q137" s="4"/>
-      <c r="R137" s="4"/>
+      <c r="J137" s="4"/>
+      <c r="K137" s="4"/>
       <c r="S137" s="4"/>
       <c r="T137" s="4"/>
       <c r="U137" s="4"/>
@@ -7478,8 +7786,10 @@
       <c r="W137" s="4"/>
       <c r="X137" s="4"/>
       <c r="Y137" s="4"/>
-    </row>
-    <row r="138" spans="1:25">
+      <c r="Z137" s="4"/>
+      <c r="AA137" s="4"/>
+    </row>
+    <row r="138" spans="1:27">
       <c r="A138" s="4"/>
       <c r="B138" s="4"/>
       <c r="C138" s="4"/>
@@ -7489,8 +7799,8 @@
       <c r="G138" s="4"/>
       <c r="H138" s="4"/>
       <c r="I138" s="4"/>
-      <c r="Q138" s="4"/>
-      <c r="R138" s="4"/>
+      <c r="J138" s="4"/>
+      <c r="K138" s="4"/>
       <c r="S138" s="4"/>
       <c r="T138" s="4"/>
       <c r="U138" s="4"/>
@@ -7498,8 +7808,10 @@
       <c r="W138" s="4"/>
       <c r="X138" s="4"/>
       <c r="Y138" s="4"/>
-    </row>
-    <row r="139" spans="1:25">
+      <c r="Z138" s="4"/>
+      <c r="AA138" s="4"/>
+    </row>
+    <row r="139" spans="1:27">
       <c r="A139" s="4"/>
       <c r="B139" s="4"/>
       <c r="C139" s="4"/>
@@ -7509,8 +7821,8 @@
       <c r="G139" s="4"/>
       <c r="H139" s="4"/>
       <c r="I139" s="4"/>
-      <c r="Q139" s="4"/>
-      <c r="R139" s="4"/>
+      <c r="J139" s="4"/>
+      <c r="K139" s="4"/>
       <c r="S139" s="4"/>
       <c r="T139" s="4"/>
       <c r="U139" s="4"/>
@@ -7518,8 +7830,10 @@
       <c r="W139" s="4"/>
       <c r="X139" s="4"/>
       <c r="Y139" s="4"/>
-    </row>
-    <row r="140" spans="1:25">
+      <c r="Z139" s="4"/>
+      <c r="AA139" s="4"/>
+    </row>
+    <row r="140" spans="1:27">
       <c r="A140" s="4"/>
       <c r="B140" s="4"/>
       <c r="C140" s="4"/>
@@ -7529,8 +7843,8 @@
       <c r="G140" s="4"/>
       <c r="H140" s="4"/>
       <c r="I140" s="4"/>
-      <c r="Q140" s="4"/>
-      <c r="R140" s="4"/>
+      <c r="J140" s="4"/>
+      <c r="K140" s="4"/>
       <c r="S140" s="4"/>
       <c r="T140" s="4"/>
       <c r="U140" s="4"/>
@@ -7538,8 +7852,10 @@
       <c r="W140" s="4"/>
       <c r="X140" s="4"/>
       <c r="Y140" s="4"/>
-    </row>
-    <row r="141" spans="1:25">
+      <c r="Z140" s="4"/>
+      <c r="AA140" s="4"/>
+    </row>
+    <row r="141" spans="1:27">
       <c r="A141" s="4"/>
       <c r="B141" s="4"/>
       <c r="C141" s="4"/>
@@ -7549,8 +7865,8 @@
       <c r="G141" s="4"/>
       <c r="H141" s="4"/>
       <c r="I141" s="4"/>
-      <c r="Q141" s="4"/>
-      <c r="R141" s="4"/>
+      <c r="J141" s="4"/>
+      <c r="K141" s="4"/>
       <c r="S141" s="4"/>
       <c r="T141" s="4"/>
       <c r="U141" s="4"/>
@@ -7558,8 +7874,10 @@
       <c r="W141" s="4"/>
       <c r="X141" s="4"/>
       <c r="Y141" s="4"/>
-    </row>
-    <row r="142" spans="1:25">
+      <c r="Z141" s="4"/>
+      <c r="AA141" s="4"/>
+    </row>
+    <row r="142" spans="1:27">
       <c r="A142" s="4"/>
       <c r="B142" s="4"/>
       <c r="C142" s="4"/>
@@ -7569,8 +7887,8 @@
       <c r="G142" s="4"/>
       <c r="H142" s="4"/>
       <c r="I142" s="4"/>
-      <c r="Q142" s="4"/>
-      <c r="R142" s="4"/>
+      <c r="J142" s="4"/>
+      <c r="K142" s="4"/>
       <c r="S142" s="4"/>
       <c r="T142" s="4"/>
       <c r="U142" s="4"/>
@@ -7578,8 +7896,10 @@
       <c r="W142" s="4"/>
       <c r="X142" s="4"/>
       <c r="Y142" s="4"/>
-    </row>
-    <row r="143" spans="1:25">
+      <c r="Z142" s="4"/>
+      <c r="AA142" s="4"/>
+    </row>
+    <row r="143" spans="1:27">
       <c r="A143" s="4"/>
       <c r="B143" s="4"/>
       <c r="C143" s="4"/>
@@ -7589,8 +7909,8 @@
       <c r="G143" s="4"/>
       <c r="H143" s="4"/>
       <c r="I143" s="4"/>
-      <c r="Q143" s="4"/>
-      <c r="R143" s="4"/>
+      <c r="J143" s="4"/>
+      <c r="K143" s="4"/>
       <c r="S143" s="4"/>
       <c r="T143" s="4"/>
       <c r="U143" s="4"/>
@@ -7598,8 +7918,10 @@
       <c r="W143" s="4"/>
       <c r="X143" s="4"/>
       <c r="Y143" s="4"/>
-    </row>
-    <row r="144" spans="1:25">
+      <c r="Z143" s="4"/>
+      <c r="AA143" s="4"/>
+    </row>
+    <row r="144" spans="1:27">
       <c r="A144" s="4"/>
       <c r="B144" s="4"/>
       <c r="C144" s="4"/>
@@ -7609,8 +7931,8 @@
       <c r="G144" s="4"/>
       <c r="H144" s="4"/>
       <c r="I144" s="4"/>
-      <c r="Q144" s="4"/>
-      <c r="R144" s="4"/>
+      <c r="J144" s="4"/>
+      <c r="K144" s="4"/>
       <c r="S144" s="4"/>
       <c r="T144" s="4"/>
       <c r="U144" s="4"/>
@@ -7618,8 +7940,10 @@
       <c r="W144" s="4"/>
       <c r="X144" s="4"/>
       <c r="Y144" s="4"/>
-    </row>
-    <row r="145" spans="1:25">
+      <c r="Z144" s="4"/>
+      <c r="AA144" s="4"/>
+    </row>
+    <row r="145" spans="1:27">
       <c r="A145" s="4"/>
       <c r="B145" s="4"/>
       <c r="C145" s="4"/>
@@ -7629,8 +7953,8 @@
       <c r="G145" s="4"/>
       <c r="H145" s="4"/>
       <c r="I145" s="4"/>
-      <c r="Q145" s="4"/>
-      <c r="R145" s="4"/>
+      <c r="J145" s="4"/>
+      <c r="K145" s="4"/>
       <c r="S145" s="4"/>
       <c r="T145" s="4"/>
       <c r="U145" s="4"/>
@@ -7638,8 +7962,10 @@
       <c r="W145" s="4"/>
       <c r="X145" s="4"/>
       <c r="Y145" s="4"/>
-    </row>
-    <row r="146" spans="1:25">
+      <c r="Z145" s="4"/>
+      <c r="AA145" s="4"/>
+    </row>
+    <row r="146" spans="1:27">
       <c r="A146" s="4"/>
       <c r="B146" s="4"/>
       <c r="C146" s="4"/>
@@ -7649,8 +7975,8 @@
       <c r="G146" s="4"/>
       <c r="H146" s="4"/>
       <c r="I146" s="4"/>
-      <c r="Q146" s="4"/>
-      <c r="R146" s="4"/>
+      <c r="J146" s="4"/>
+      <c r="K146" s="4"/>
       <c r="S146" s="4"/>
       <c r="T146" s="4"/>
       <c r="U146" s="4"/>
@@ -7658,8 +7984,10 @@
       <c r="W146" s="4"/>
       <c r="X146" s="4"/>
       <c r="Y146" s="4"/>
-    </row>
-    <row r="147" spans="1:25">
+      <c r="Z146" s="4"/>
+      <c r="AA146" s="4"/>
+    </row>
+    <row r="147" spans="1:27">
       <c r="A147" s="4"/>
       <c r="B147" s="4"/>
       <c r="C147" s="4"/>
@@ -7669,8 +7997,8 @@
       <c r="G147" s="4"/>
       <c r="H147" s="4"/>
       <c r="I147" s="4"/>
-      <c r="Q147" s="4"/>
-      <c r="R147" s="4"/>
+      <c r="J147" s="4"/>
+      <c r="K147" s="4"/>
       <c r="S147" s="4"/>
       <c r="T147" s="4"/>
       <c r="U147" s="4"/>
@@ -7678,8 +8006,10 @@
       <c r="W147" s="4"/>
       <c r="X147" s="4"/>
       <c r="Y147" s="4"/>
-    </row>
-    <row r="148" spans="1:25">
+      <c r="Z147" s="4"/>
+      <c r="AA147" s="4"/>
+    </row>
+    <row r="148" spans="1:27">
       <c r="A148" s="4"/>
       <c r="B148" s="4"/>
       <c r="C148" s="4"/>
@@ -7689,8 +8019,8 @@
       <c r="G148" s="4"/>
       <c r="H148" s="4"/>
       <c r="I148" s="4"/>
-      <c r="Q148" s="4"/>
-      <c r="R148" s="4"/>
+      <c r="J148" s="4"/>
+      <c r="K148" s="4"/>
       <c r="S148" s="4"/>
       <c r="T148" s="4"/>
       <c r="U148" s="4"/>
@@ -7698,8 +8028,10 @@
       <c r="W148" s="4"/>
       <c r="X148" s="4"/>
       <c r="Y148" s="4"/>
-    </row>
-    <row r="149" spans="1:25">
+      <c r="Z148" s="4"/>
+      <c r="AA148" s="4"/>
+    </row>
+    <row r="149" spans="1:27">
       <c r="A149" s="4"/>
       <c r="B149" s="4"/>
       <c r="C149" s="4"/>
@@ -7709,8 +8041,8 @@
       <c r="G149" s="4"/>
       <c r="H149" s="4"/>
       <c r="I149" s="4"/>
-      <c r="Q149" s="4"/>
-      <c r="R149" s="4"/>
+      <c r="J149" s="4"/>
+      <c r="K149" s="4"/>
       <c r="S149" s="4"/>
       <c r="T149" s="4"/>
       <c r="U149" s="4"/>
@@ -7718,8 +8050,10 @@
       <c r="W149" s="4"/>
       <c r="X149" s="4"/>
       <c r="Y149" s="4"/>
-    </row>
-    <row r="150" spans="1:25">
+      <c r="Z149" s="4"/>
+      <c r="AA149" s="4"/>
+    </row>
+    <row r="150" spans="1:27">
       <c r="A150" s="4"/>
       <c r="B150" s="4"/>
       <c r="C150" s="4"/>
@@ -7729,8 +8063,8 @@
       <c r="G150" s="4"/>
       <c r="H150" s="4"/>
       <c r="I150" s="4"/>
-      <c r="Q150" s="4"/>
-      <c r="R150" s="4"/>
+      <c r="J150" s="4"/>
+      <c r="K150" s="4"/>
       <c r="S150" s="4"/>
       <c r="T150" s="4"/>
       <c r="U150" s="4"/>
@@ -7738,8 +8072,10 @@
       <c r="W150" s="4"/>
       <c r="X150" s="4"/>
       <c r="Y150" s="4"/>
-    </row>
-    <row r="151" spans="1:25">
+      <c r="Z150" s="4"/>
+      <c r="AA150" s="4"/>
+    </row>
+    <row r="151" spans="1:27">
       <c r="A151" s="4"/>
       <c r="B151" s="4"/>
       <c r="C151" s="4"/>
@@ -7749,8 +8085,8 @@
       <c r="G151" s="4"/>
       <c r="H151" s="4"/>
       <c r="I151" s="4"/>
-      <c r="Q151" s="4"/>
-      <c r="R151" s="4"/>
+      <c r="J151" s="4"/>
+      <c r="K151" s="4"/>
       <c r="S151" s="4"/>
       <c r="T151" s="4"/>
       <c r="U151" s="4"/>
@@ -7758,8 +8094,10 @@
       <c r="W151" s="4"/>
       <c r="X151" s="4"/>
       <c r="Y151" s="4"/>
-    </row>
-    <row r="152" spans="1:25">
+      <c r="Z151" s="4"/>
+      <c r="AA151" s="4"/>
+    </row>
+    <row r="152" spans="1:27">
       <c r="A152" s="4"/>
       <c r="B152" s="4"/>
       <c r="C152" s="4"/>
@@ -7769,8 +8107,8 @@
       <c r="G152" s="4"/>
       <c r="H152" s="4"/>
       <c r="I152" s="4"/>
-      <c r="Q152" s="4"/>
-      <c r="R152" s="4"/>
+      <c r="J152" s="4"/>
+      <c r="K152" s="4"/>
       <c r="S152" s="4"/>
       <c r="T152" s="4"/>
       <c r="U152" s="4"/>
@@ -7778,8 +8116,10 @@
       <c r="W152" s="4"/>
       <c r="X152" s="4"/>
       <c r="Y152" s="4"/>
-    </row>
-    <row r="153" spans="1:25">
+      <c r="Z152" s="4"/>
+      <c r="AA152" s="4"/>
+    </row>
+    <row r="153" spans="1:27">
       <c r="A153" s="4"/>
       <c r="B153" s="4"/>
       <c r="C153" s="4"/>
@@ -7789,8 +8129,8 @@
       <c r="G153" s="4"/>
       <c r="H153" s="4"/>
       <c r="I153" s="4"/>
-      <c r="Q153" s="4"/>
-      <c r="R153" s="4"/>
+      <c r="J153" s="4"/>
+      <c r="K153" s="4"/>
       <c r="S153" s="4"/>
       <c r="T153" s="4"/>
       <c r="U153" s="4"/>
@@ -7798,8 +8138,10 @@
       <c r="W153" s="4"/>
       <c r="X153" s="4"/>
       <c r="Y153" s="4"/>
-    </row>
-    <row r="154" spans="1:25">
+      <c r="Z153" s="4"/>
+      <c r="AA153" s="4"/>
+    </row>
+    <row r="154" spans="1:27">
       <c r="A154" s="4"/>
       <c r="B154" s="4"/>
       <c r="C154" s="4"/>
@@ -7809,8 +8151,8 @@
       <c r="G154" s="4"/>
       <c r="H154" s="4"/>
       <c r="I154" s="4"/>
-      <c r="Q154" s="4"/>
-      <c r="R154" s="4"/>
+      <c r="J154" s="4"/>
+      <c r="K154" s="4"/>
       <c r="S154" s="4"/>
       <c r="T154" s="4"/>
       <c r="U154" s="4"/>
@@ -7818,8 +8160,10 @@
       <c r="W154" s="4"/>
       <c r="X154" s="4"/>
       <c r="Y154" s="4"/>
-    </row>
-    <row r="155" spans="1:25">
+      <c r="Z154" s="4"/>
+      <c r="AA154" s="4"/>
+    </row>
+    <row r="155" spans="1:27">
       <c r="A155" s="4"/>
       <c r="B155" s="4"/>
       <c r="C155" s="4"/>
@@ -7829,8 +8173,8 @@
       <c r="G155" s="4"/>
       <c r="H155" s="4"/>
       <c r="I155" s="4"/>
-      <c r="Q155" s="4"/>
-      <c r="R155" s="4"/>
+      <c r="J155" s="4"/>
+      <c r="K155" s="4"/>
       <c r="S155" s="4"/>
       <c r="T155" s="4"/>
       <c r="U155" s="4"/>
@@ -7838,8 +8182,10 @@
       <c r="W155" s="4"/>
       <c r="X155" s="4"/>
       <c r="Y155" s="4"/>
-    </row>
-    <row r="156" spans="1:25">
+      <c r="Z155" s="4"/>
+      <c r="AA155" s="4"/>
+    </row>
+    <row r="156" spans="1:27">
       <c r="A156" s="4"/>
       <c r="B156" s="4"/>
       <c r="C156" s="4"/>
@@ -7849,8 +8195,8 @@
       <c r="G156" s="4"/>
       <c r="H156" s="4"/>
       <c r="I156" s="4"/>
-      <c r="Q156" s="4"/>
-      <c r="R156" s="4"/>
+      <c r="J156" s="4"/>
+      <c r="K156" s="4"/>
       <c r="S156" s="4"/>
       <c r="T156" s="4"/>
       <c r="U156" s="4"/>
@@ -7858,8 +8204,10 @@
       <c r="W156" s="4"/>
       <c r="X156" s="4"/>
       <c r="Y156" s="4"/>
-    </row>
-    <row r="157" spans="1:25">
+      <c r="Z156" s="4"/>
+      <c r="AA156" s="4"/>
+    </row>
+    <row r="157" spans="1:27">
       <c r="A157" s="4"/>
       <c r="B157" s="4"/>
       <c r="C157" s="4"/>
@@ -7869,8 +8217,8 @@
       <c r="G157" s="4"/>
       <c r="H157" s="4"/>
       <c r="I157" s="4"/>
-      <c r="Q157" s="4"/>
-      <c r="R157" s="4"/>
+      <c r="J157" s="4"/>
+      <c r="K157" s="4"/>
       <c r="S157" s="4"/>
       <c r="T157" s="4"/>
       <c r="U157" s="4"/>
@@ -7878,8 +8226,10 @@
       <c r="W157" s="4"/>
       <c r="X157" s="4"/>
       <c r="Y157" s="4"/>
-    </row>
-    <row r="158" spans="1:25">
+      <c r="Z157" s="4"/>
+      <c r="AA157" s="4"/>
+    </row>
+    <row r="158" spans="1:27">
       <c r="A158" s="4"/>
       <c r="B158" s="4"/>
       <c r="C158" s="4"/>
@@ -7889,8 +8239,8 @@
       <c r="G158" s="4"/>
       <c r="H158" s="4"/>
       <c r="I158" s="4"/>
-      <c r="Q158" s="4"/>
-      <c r="R158" s="4"/>
+      <c r="J158" s="4"/>
+      <c r="K158" s="4"/>
       <c r="S158" s="4"/>
       <c r="T158" s="4"/>
       <c r="U158" s="4"/>
@@ -7898,8 +8248,10 @@
       <c r="W158" s="4"/>
       <c r="X158" s="4"/>
       <c r="Y158" s="4"/>
-    </row>
-    <row r="159" spans="1:25">
+      <c r="Z158" s="4"/>
+      <c r="AA158" s="4"/>
+    </row>
+    <row r="159" spans="1:27">
       <c r="A159" s="4"/>
       <c r="B159" s="4"/>
       <c r="C159" s="4"/>
@@ -7909,8 +8261,8 @@
       <c r="G159" s="4"/>
       <c r="H159" s="4"/>
       <c r="I159" s="4"/>
-      <c r="Q159" s="4"/>
-      <c r="R159" s="4"/>
+      <c r="J159" s="4"/>
+      <c r="K159" s="4"/>
       <c r="S159" s="4"/>
       <c r="T159" s="4"/>
       <c r="U159" s="4"/>
@@ -7918,8 +8270,10 @@
       <c r="W159" s="4"/>
       <c r="X159" s="4"/>
       <c r="Y159" s="4"/>
-    </row>
-    <row r="160" spans="1:25">
+      <c r="Z159" s="4"/>
+      <c r="AA159" s="4"/>
+    </row>
+    <row r="160" spans="1:27">
       <c r="A160" s="4"/>
       <c r="B160" s="4"/>
       <c r="C160" s="4"/>
@@ -7929,8 +8283,8 @@
       <c r="G160" s="4"/>
       <c r="H160" s="4"/>
       <c r="I160" s="4"/>
-      <c r="Q160" s="4"/>
-      <c r="R160" s="4"/>
+      <c r="J160" s="4"/>
+      <c r="K160" s="4"/>
       <c r="S160" s="4"/>
       <c r="T160" s="4"/>
       <c r="U160" s="4"/>
@@ -7938,8 +8292,10 @@
       <c r="W160" s="4"/>
       <c r="X160" s="4"/>
       <c r="Y160" s="4"/>
-    </row>
-    <row r="161" spans="1:25">
+      <c r="Z160" s="4"/>
+      <c r="AA160" s="4"/>
+    </row>
+    <row r="161" spans="1:27">
       <c r="A161" s="4"/>
       <c r="B161" s="4"/>
       <c r="C161" s="4"/>
@@ -7949,8 +8305,8 @@
       <c r="G161" s="4"/>
       <c r="H161" s="4"/>
       <c r="I161" s="4"/>
-      <c r="Q161" s="4"/>
-      <c r="R161" s="4"/>
+      <c r="J161" s="4"/>
+      <c r="K161" s="4"/>
       <c r="S161" s="4"/>
       <c r="T161" s="4"/>
       <c r="U161" s="4"/>
@@ -7958,8 +8314,10 @@
       <c r="W161" s="4"/>
       <c r="X161" s="4"/>
       <c r="Y161" s="4"/>
-    </row>
-    <row r="162" spans="1:25">
+      <c r="Z161" s="4"/>
+      <c r="AA161" s="4"/>
+    </row>
+    <row r="162" spans="1:27">
       <c r="A162" s="4"/>
       <c r="B162" s="4"/>
       <c r="C162" s="4"/>
@@ -7969,8 +8327,8 @@
       <c r="G162" s="4"/>
       <c r="H162" s="4"/>
       <c r="I162" s="4"/>
-      <c r="Q162" s="4"/>
-      <c r="R162" s="4"/>
+      <c r="J162" s="4"/>
+      <c r="K162" s="4"/>
       <c r="S162" s="4"/>
       <c r="T162" s="4"/>
       <c r="U162" s="4"/>
@@ -7978,8 +8336,10 @@
       <c r="W162" s="4"/>
       <c r="X162" s="4"/>
       <c r="Y162" s="4"/>
-    </row>
-    <row r="163" spans="1:25">
+      <c r="Z162" s="4"/>
+      <c r="AA162" s="4"/>
+    </row>
+    <row r="163" spans="1:27">
       <c r="A163" s="4"/>
       <c r="B163" s="4"/>
       <c r="C163" s="4"/>
@@ -7989,8 +8349,8 @@
       <c r="G163" s="4"/>
       <c r="H163" s="4"/>
       <c r="I163" s="4"/>
-      <c r="Q163" s="4"/>
-      <c r="R163" s="4"/>
+      <c r="J163" s="4"/>
+      <c r="K163" s="4"/>
       <c r="S163" s="4"/>
       <c r="T163" s="4"/>
       <c r="U163" s="4"/>
@@ -7998,8 +8358,10 @@
       <c r="W163" s="4"/>
       <c r="X163" s="4"/>
       <c r="Y163" s="4"/>
-    </row>
-    <row r="164" spans="1:25">
+      <c r="Z163" s="4"/>
+      <c r="AA163" s="4"/>
+    </row>
+    <row r="164" spans="1:27">
       <c r="A164" s="4"/>
       <c r="B164" s="4"/>
       <c r="C164" s="4"/>
@@ -8009,8 +8371,8 @@
       <c r="G164" s="4"/>
       <c r="H164" s="4"/>
       <c r="I164" s="4"/>
-      <c r="Q164" s="4"/>
-      <c r="R164" s="4"/>
+      <c r="J164" s="4"/>
+      <c r="K164" s="4"/>
       <c r="S164" s="4"/>
       <c r="T164" s="4"/>
       <c r="U164" s="4"/>
@@ -8018,8 +8380,10 @@
       <c r="W164" s="4"/>
       <c r="X164" s="4"/>
       <c r="Y164" s="4"/>
-    </row>
-    <row r="165" spans="1:25">
+      <c r="Z164" s="4"/>
+      <c r="AA164" s="4"/>
+    </row>
+    <row r="165" spans="1:27">
       <c r="A165" s="4"/>
       <c r="B165" s="4"/>
       <c r="C165" s="4"/>
@@ -8029,8 +8393,8 @@
       <c r="G165" s="4"/>
       <c r="H165" s="4"/>
       <c r="I165" s="4"/>
-      <c r="Q165" s="4"/>
-      <c r="R165" s="4"/>
+      <c r="J165" s="4"/>
+      <c r="K165" s="4"/>
       <c r="S165" s="4"/>
       <c r="T165" s="4"/>
       <c r="U165" s="4"/>
@@ -8038,8 +8402,10 @@
       <c r="W165" s="4"/>
       <c r="X165" s="4"/>
       <c r="Y165" s="4"/>
-    </row>
-    <row r="166" spans="1:25">
+      <c r="Z165" s="4"/>
+      <c r="AA165" s="4"/>
+    </row>
+    <row r="166" spans="1:27">
       <c r="A166" s="4"/>
       <c r="B166" s="4"/>
       <c r="C166" s="4"/>
@@ -8049,8 +8415,8 @@
       <c r="G166" s="4"/>
       <c r="H166" s="4"/>
       <c r="I166" s="4"/>
-      <c r="Q166" s="4"/>
-      <c r="R166" s="4"/>
+      <c r="J166" s="4"/>
+      <c r="K166" s="4"/>
       <c r="S166" s="4"/>
       <c r="T166" s="4"/>
       <c r="U166" s="4"/>
@@ -8058,8 +8424,10 @@
       <c r="W166" s="4"/>
       <c r="X166" s="4"/>
       <c r="Y166" s="4"/>
-    </row>
-    <row r="167" spans="1:25">
+      <c r="Z166" s="4"/>
+      <c r="AA166" s="4"/>
+    </row>
+    <row r="167" spans="1:27">
       <c r="A167" s="4"/>
       <c r="B167" s="4"/>
       <c r="C167" s="4"/>
@@ -8069,8 +8437,8 @@
       <c r="G167" s="4"/>
       <c r="H167" s="4"/>
       <c r="I167" s="4"/>
-      <c r="Q167" s="4"/>
-      <c r="R167" s="4"/>
+      <c r="J167" s="4"/>
+      <c r="K167" s="4"/>
       <c r="S167" s="4"/>
       <c r="T167" s="4"/>
       <c r="U167" s="4"/>
@@ -8078,8 +8446,10 @@
       <c r="W167" s="4"/>
       <c r="X167" s="4"/>
       <c r="Y167" s="4"/>
-    </row>
-    <row r="168" spans="1:25">
+      <c r="Z167" s="4"/>
+      <c r="AA167" s="4"/>
+    </row>
+    <row r="168" spans="1:27">
       <c r="A168" s="4"/>
       <c r="B168" s="4"/>
       <c r="C168" s="4"/>
@@ -8089,8 +8459,8 @@
       <c r="G168" s="4"/>
       <c r="H168" s="4"/>
       <c r="I168" s="4"/>
-      <c r="Q168" s="4"/>
-      <c r="R168" s="4"/>
+      <c r="J168" s="4"/>
+      <c r="K168" s="4"/>
       <c r="S168" s="4"/>
       <c r="T168" s="4"/>
       <c r="U168" s="4"/>
@@ -8098,8 +8468,10 @@
       <c r="W168" s="4"/>
       <c r="X168" s="4"/>
       <c r="Y168" s="4"/>
-    </row>
-    <row r="169" spans="1:25">
+      <c r="Z168" s="4"/>
+      <c r="AA168" s="4"/>
+    </row>
+    <row r="169" spans="1:27">
       <c r="A169" s="4"/>
       <c r="B169" s="4"/>
       <c r="C169" s="4"/>
@@ -8109,8 +8481,8 @@
       <c r="G169" s="4"/>
       <c r="H169" s="4"/>
       <c r="I169" s="4"/>
-      <c r="Q169" s="4"/>
-      <c r="R169" s="4"/>
+      <c r="J169" s="4"/>
+      <c r="K169" s="4"/>
       <c r="S169" s="4"/>
       <c r="T169" s="4"/>
       <c r="U169" s="4"/>
@@ -8118,8 +8490,10 @@
       <c r="W169" s="4"/>
       <c r="X169" s="4"/>
       <c r="Y169" s="4"/>
-    </row>
-    <row r="170" spans="1:25">
+      <c r="Z169" s="4"/>
+      <c r="AA169" s="4"/>
+    </row>
+    <row r="170" spans="1:27">
       <c r="A170" s="4"/>
       <c r="B170" s="4"/>
       <c r="C170" s="4"/>
@@ -8129,8 +8503,8 @@
       <c r="G170" s="4"/>
       <c r="H170" s="4"/>
       <c r="I170" s="4"/>
-      <c r="Q170" s="4"/>
-      <c r="R170" s="4"/>
+      <c r="J170" s="4"/>
+      <c r="K170" s="4"/>
       <c r="S170" s="4"/>
       <c r="T170" s="4"/>
       <c r="U170" s="4"/>
@@ -8138,8 +8512,10 @@
       <c r="W170" s="4"/>
       <c r="X170" s="4"/>
       <c r="Y170" s="4"/>
-    </row>
-    <row r="171" spans="1:25">
+      <c r="Z170" s="4"/>
+      <c r="AA170" s="4"/>
+    </row>
+    <row r="171" spans="1:27">
       <c r="A171" s="4"/>
       <c r="B171" s="4"/>
       <c r="C171" s="4"/>
@@ -8149,8 +8525,8 @@
       <c r="G171" s="4"/>
       <c r="H171" s="4"/>
       <c r="I171" s="4"/>
-      <c r="Q171" s="4"/>
-      <c r="R171" s="4"/>
+      <c r="J171" s="4"/>
+      <c r="K171" s="4"/>
       <c r="S171" s="4"/>
       <c r="T171" s="4"/>
       <c r="U171" s="4"/>
@@ -8158,8 +8534,10 @@
       <c r="W171" s="4"/>
       <c r="X171" s="4"/>
       <c r="Y171" s="4"/>
-    </row>
-    <row r="172" spans="1:25">
+      <c r="Z171" s="4"/>
+      <c r="AA171" s="4"/>
+    </row>
+    <row r="172" spans="1:27">
       <c r="A172" s="4"/>
       <c r="B172" s="4"/>
       <c r="C172" s="4"/>
@@ -8169,8 +8547,8 @@
       <c r="G172" s="4"/>
       <c r="H172" s="4"/>
       <c r="I172" s="4"/>
-      <c r="Q172" s="4"/>
-      <c r="R172" s="4"/>
+      <c r="J172" s="4"/>
+      <c r="K172" s="4"/>
       <c r="S172" s="4"/>
       <c r="T172" s="4"/>
       <c r="U172" s="4"/>
@@ -8178,8 +8556,10 @@
       <c r="W172" s="4"/>
       <c r="X172" s="4"/>
       <c r="Y172" s="4"/>
-    </row>
-    <row r="173" spans="1:25">
+      <c r="Z172" s="4"/>
+      <c r="AA172" s="4"/>
+    </row>
+    <row r="173" spans="1:27">
       <c r="A173" s="4"/>
       <c r="B173" s="4"/>
       <c r="C173" s="4"/>
@@ -8189,8 +8569,8 @@
       <c r="G173" s="4"/>
       <c r="H173" s="4"/>
       <c r="I173" s="4"/>
-      <c r="Q173" s="4"/>
-      <c r="R173" s="4"/>
+      <c r="J173" s="4"/>
+      <c r="K173" s="4"/>
       <c r="S173" s="4"/>
       <c r="T173" s="4"/>
       <c r="U173" s="4"/>
@@ -8198,8 +8578,10 @@
       <c r="W173" s="4"/>
       <c r="X173" s="4"/>
       <c r="Y173" s="4"/>
-    </row>
-    <row r="174" spans="1:25">
+      <c r="Z173" s="4"/>
+      <c r="AA173" s="4"/>
+    </row>
+    <row r="174" spans="1:27">
       <c r="A174" s="4"/>
       <c r="B174" s="4"/>
       <c r="C174" s="4"/>
@@ -8209,8 +8591,8 @@
       <c r="G174" s="4"/>
       <c r="H174" s="4"/>
       <c r="I174" s="4"/>
-      <c r="Q174" s="4"/>
-      <c r="R174" s="4"/>
+      <c r="J174" s="4"/>
+      <c r="K174" s="4"/>
       <c r="S174" s="4"/>
       <c r="T174" s="4"/>
       <c r="U174" s="4"/>
@@ -8218,8 +8600,10 @@
       <c r="W174" s="4"/>
       <c r="X174" s="4"/>
       <c r="Y174" s="4"/>
-    </row>
-    <row r="175" spans="1:25">
+      <c r="Z174" s="4"/>
+      <c r="AA174" s="4"/>
+    </row>
+    <row r="175" spans="1:27">
       <c r="A175" s="4"/>
       <c r="B175" s="4"/>
       <c r="C175" s="4"/>
@@ -8229,8 +8613,8 @@
       <c r="G175" s="4"/>
       <c r="H175" s="4"/>
       <c r="I175" s="4"/>
-      <c r="Q175" s="4"/>
-      <c r="R175" s="4"/>
+      <c r="J175" s="4"/>
+      <c r="K175" s="4"/>
       <c r="S175" s="4"/>
       <c r="T175" s="4"/>
       <c r="U175" s="4"/>
@@ -8238,8 +8622,10 @@
       <c r="W175" s="4"/>
       <c r="X175" s="4"/>
       <c r="Y175" s="4"/>
-    </row>
-    <row r="176" spans="1:25">
+      <c r="Z175" s="4"/>
+      <c r="AA175" s="4"/>
+    </row>
+    <row r="176" spans="1:27">
       <c r="A176" s="4"/>
       <c r="B176" s="4"/>
       <c r="C176" s="4"/>
@@ -8249,8 +8635,8 @@
       <c r="G176" s="4"/>
       <c r="H176" s="4"/>
       <c r="I176" s="4"/>
-      <c r="Q176" s="4"/>
-      <c r="R176" s="4"/>
+      <c r="J176" s="4"/>
+      <c r="K176" s="4"/>
       <c r="S176" s="4"/>
       <c r="T176" s="4"/>
       <c r="U176" s="4"/>
@@ -8258,8 +8644,10 @@
       <c r="W176" s="4"/>
       <c r="X176" s="4"/>
       <c r="Y176" s="4"/>
-    </row>
-    <row r="177" spans="1:25">
+      <c r="Z176" s="4"/>
+      <c r="AA176" s="4"/>
+    </row>
+    <row r="177" spans="1:27">
       <c r="A177" s="4"/>
       <c r="B177" s="4"/>
       <c r="C177" s="4"/>
@@ -8269,8 +8657,8 @@
       <c r="G177" s="4"/>
       <c r="H177" s="4"/>
       <c r="I177" s="4"/>
-      <c r="Q177" s="4"/>
-      <c r="R177" s="4"/>
+      <c r="J177" s="4"/>
+      <c r="K177" s="4"/>
       <c r="S177" s="4"/>
       <c r="T177" s="4"/>
       <c r="U177" s="4"/>
@@ -8278,8 +8666,10 @@
       <c r="W177" s="4"/>
       <c r="X177" s="4"/>
       <c r="Y177" s="4"/>
-    </row>
-    <row r="178" spans="1:25">
+      <c r="Z177" s="4"/>
+      <c r="AA177" s="4"/>
+    </row>
+    <row r="178" spans="1:27">
       <c r="A178" s="4"/>
       <c r="B178" s="4"/>
       <c r="C178" s="4"/>
@@ -8289,8 +8679,8 @@
       <c r="G178" s="4"/>
       <c r="H178" s="4"/>
       <c r="I178" s="4"/>
-      <c r="Q178" s="4"/>
-      <c r="R178" s="4"/>
+      <c r="J178" s="4"/>
+      <c r="K178" s="4"/>
       <c r="S178" s="4"/>
       <c r="T178" s="4"/>
       <c r="U178" s="4"/>
@@ -8298,8 +8688,10 @@
       <c r="W178" s="4"/>
       <c r="X178" s="4"/>
       <c r="Y178" s="4"/>
-    </row>
-    <row r="179" spans="1:25">
+      <c r="Z178" s="4"/>
+      <c r="AA178" s="4"/>
+    </row>
+    <row r="179" spans="1:27">
       <c r="A179" s="4"/>
       <c r="B179" s="4"/>
       <c r="C179" s="4"/>
@@ -8309,8 +8701,8 @@
       <c r="G179" s="4"/>
       <c r="H179" s="4"/>
       <c r="I179" s="4"/>
-      <c r="Q179" s="4"/>
-      <c r="R179" s="4"/>
+      <c r="J179" s="4"/>
+      <c r="K179" s="4"/>
       <c r="S179" s="4"/>
       <c r="T179" s="4"/>
       <c r="U179" s="4"/>
@@ -8318,8 +8710,10 @@
       <c r="W179" s="4"/>
       <c r="X179" s="4"/>
       <c r="Y179" s="4"/>
-    </row>
-    <row r="180" spans="1:25">
+      <c r="Z179" s="4"/>
+      <c r="AA179" s="4"/>
+    </row>
+    <row r="180" spans="1:27">
       <c r="A180" s="4"/>
       <c r="B180" s="4"/>
       <c r="C180" s="4"/>
@@ -8329,8 +8723,8 @@
       <c r="G180" s="4"/>
       <c r="H180" s="4"/>
       <c r="I180" s="4"/>
-      <c r="Q180" s="4"/>
-      <c r="R180" s="4"/>
+      <c r="J180" s="4"/>
+      <c r="K180" s="4"/>
       <c r="S180" s="4"/>
       <c r="T180" s="4"/>
       <c r="U180" s="4"/>
@@ -8338,8 +8732,10 @@
       <c r="W180" s="4"/>
       <c r="X180" s="4"/>
       <c r="Y180" s="4"/>
-    </row>
-    <row r="181" spans="1:25">
+      <c r="Z180" s="4"/>
+      <c r="AA180" s="4"/>
+    </row>
+    <row r="181" spans="1:27">
       <c r="A181" s="4"/>
       <c r="B181" s="4"/>
       <c r="C181" s="4"/>
@@ -8349,8 +8745,8 @@
       <c r="G181" s="4"/>
       <c r="H181" s="4"/>
       <c r="I181" s="4"/>
-      <c r="Q181" s="4"/>
-      <c r="R181" s="4"/>
+      <c r="J181" s="4"/>
+      <c r="K181" s="4"/>
       <c r="S181" s="4"/>
       <c r="T181" s="4"/>
       <c r="U181" s="4"/>
@@ -8358,8 +8754,10 @@
       <c r="W181" s="4"/>
       <c r="X181" s="4"/>
       <c r="Y181" s="4"/>
-    </row>
-    <row r="182" spans="1:25">
+      <c r="Z181" s="4"/>
+      <c r="AA181" s="4"/>
+    </row>
+    <row r="182" spans="1:27">
       <c r="A182" s="4"/>
       <c r="B182" s="4"/>
       <c r="C182" s="4"/>
@@ -8369,8 +8767,8 @@
       <c r="G182" s="4"/>
       <c r="H182" s="4"/>
       <c r="I182" s="4"/>
-      <c r="Q182" s="4"/>
-      <c r="R182" s="4"/>
+      <c r="J182" s="4"/>
+      <c r="K182" s="4"/>
       <c r="S182" s="4"/>
       <c r="T182" s="4"/>
       <c r="U182" s="4"/>
@@ -8378,8 +8776,10 @@
       <c r="W182" s="4"/>
       <c r="X182" s="4"/>
       <c r="Y182" s="4"/>
-    </row>
-    <row r="183" spans="1:25">
+      <c r="Z182" s="4"/>
+      <c r="AA182" s="4"/>
+    </row>
+    <row r="183" spans="1:27">
       <c r="A183" s="4"/>
       <c r="B183" s="4"/>
       <c r="C183" s="4"/>
@@ -8389,8 +8789,8 @@
       <c r="G183" s="4"/>
       <c r="H183" s="4"/>
       <c r="I183" s="4"/>
-      <c r="Q183" s="4"/>
-      <c r="R183" s="4"/>
+      <c r="J183" s="4"/>
+      <c r="K183" s="4"/>
       <c r="S183" s="4"/>
       <c r="T183" s="4"/>
       <c r="U183" s="4"/>
@@ -8398,8 +8798,10 @@
       <c r="W183" s="4"/>
       <c r="X183" s="4"/>
       <c r="Y183" s="4"/>
-    </row>
-    <row r="184" spans="1:25">
+      <c r="Z183" s="4"/>
+      <c r="AA183" s="4"/>
+    </row>
+    <row r="184" spans="1:27">
       <c r="A184" s="4"/>
       <c r="B184" s="4"/>
       <c r="C184" s="4"/>
@@ -8409,8 +8811,8 @@
       <c r="G184" s="4"/>
       <c r="H184" s="4"/>
       <c r="I184" s="4"/>
-      <c r="Q184" s="4"/>
-      <c r="R184" s="4"/>
+      <c r="J184" s="4"/>
+      <c r="K184" s="4"/>
       <c r="S184" s="4"/>
       <c r="T184" s="4"/>
       <c r="U184" s="4"/>
@@ -8418,8 +8820,10 @@
       <c r="W184" s="4"/>
       <c r="X184" s="4"/>
       <c r="Y184" s="4"/>
-    </row>
-    <row r="185" spans="1:25">
+      <c r="Z184" s="4"/>
+      <c r="AA184" s="4"/>
+    </row>
+    <row r="185" spans="1:27">
       <c r="A185" s="4"/>
       <c r="B185" s="4"/>
       <c r="C185" s="4"/>
@@ -8429,8 +8833,8 @@
       <c r="G185" s="4"/>
       <c r="H185" s="4"/>
       <c r="I185" s="4"/>
-      <c r="Q185" s="4"/>
-      <c r="R185" s="4"/>
+      <c r="J185" s="4"/>
+      <c r="K185" s="4"/>
       <c r="S185" s="4"/>
       <c r="T185" s="4"/>
       <c r="U185" s="4"/>
@@ -8438,8 +8842,10 @@
       <c r="W185" s="4"/>
       <c r="X185" s="4"/>
       <c r="Y185" s="4"/>
-    </row>
-    <row r="186" spans="1:25">
+      <c r="Z185" s="4"/>
+      <c r="AA185" s="4"/>
+    </row>
+    <row r="186" spans="1:27">
       <c r="A186" s="4"/>
       <c r="B186" s="4"/>
       <c r="C186" s="4"/>
@@ -8449,8 +8855,8 @@
       <c r="G186" s="4"/>
       <c r="H186" s="4"/>
       <c r="I186" s="4"/>
-      <c r="Q186" s="4"/>
-      <c r="R186" s="4"/>
+      <c r="J186" s="4"/>
+      <c r="K186" s="4"/>
       <c r="S186" s="4"/>
       <c r="T186" s="4"/>
       <c r="U186" s="4"/>
@@ -8458,8 +8864,10 @@
       <c r="W186" s="4"/>
       <c r="X186" s="4"/>
       <c r="Y186" s="4"/>
-    </row>
-    <row r="187" spans="1:25">
+      <c r="Z186" s="4"/>
+      <c r="AA186" s="4"/>
+    </row>
+    <row r="187" spans="1:27">
       <c r="A187" s="4"/>
       <c r="B187" s="4"/>
       <c r="C187" s="4"/>
@@ -8469,8 +8877,8 @@
       <c r="G187" s="4"/>
       <c r="H187" s="4"/>
       <c r="I187" s="4"/>
-      <c r="Q187" s="4"/>
-      <c r="R187" s="4"/>
+      <c r="J187" s="4"/>
+      <c r="K187" s="4"/>
       <c r="S187" s="4"/>
       <c r="T187" s="4"/>
       <c r="U187" s="4"/>
@@ -8478,8 +8886,10 @@
       <c r="W187" s="4"/>
       <c r="X187" s="4"/>
       <c r="Y187" s="4"/>
-    </row>
-    <row r="188" spans="1:25">
+      <c r="Z187" s="4"/>
+      <c r="AA187" s="4"/>
+    </row>
+    <row r="188" spans="1:27">
       <c r="A188" s="4"/>
       <c r="B188" s="4"/>
       <c r="C188" s="4"/>
@@ -8489,8 +8899,8 @@
       <c r="G188" s="4"/>
       <c r="H188" s="4"/>
       <c r="I188" s="4"/>
-      <c r="Q188" s="4"/>
-      <c r="R188" s="4"/>
+      <c r="J188" s="4"/>
+      <c r="K188" s="4"/>
       <c r="S188" s="4"/>
       <c r="T188" s="4"/>
       <c r="U188" s="4"/>
@@ -8498,8 +8908,10 @@
       <c r="W188" s="4"/>
       <c r="X188" s="4"/>
       <c r="Y188" s="4"/>
-    </row>
-    <row r="189" spans="1:25">
+      <c r="Z188" s="4"/>
+      <c r="AA188" s="4"/>
+    </row>
+    <row r="189" spans="1:27">
       <c r="A189" s="4"/>
       <c r="B189" s="4"/>
       <c r="C189" s="4"/>
@@ -8509,8 +8921,8 @@
       <c r="G189" s="4"/>
       <c r="H189" s="4"/>
       <c r="I189" s="4"/>
-      <c r="Q189" s="4"/>
-      <c r="R189" s="4"/>
+      <c r="J189" s="4"/>
+      <c r="K189" s="4"/>
       <c r="S189" s="4"/>
       <c r="T189" s="4"/>
       <c r="U189" s="4"/>
@@ -8518,8 +8930,10 @@
       <c r="W189" s="4"/>
       <c r="X189" s="4"/>
       <c r="Y189" s="4"/>
-    </row>
-    <row r="190" spans="1:25">
+      <c r="Z189" s="4"/>
+      <c r="AA189" s="4"/>
+    </row>
+    <row r="190" spans="1:27">
       <c r="A190" s="4"/>
       <c r="B190" s="4"/>
       <c r="C190" s="4"/>
@@ -8529,8 +8943,8 @@
       <c r="G190" s="4"/>
       <c r="H190" s="4"/>
       <c r="I190" s="4"/>
-      <c r="Q190" s="4"/>
-      <c r="R190" s="4"/>
+      <c r="J190" s="4"/>
+      <c r="K190" s="4"/>
       <c r="S190" s="4"/>
       <c r="T190" s="4"/>
       <c r="U190" s="4"/>
@@ -8538,8 +8952,10 @@
       <c r="W190" s="4"/>
       <c r="X190" s="4"/>
       <c r="Y190" s="4"/>
-    </row>
-    <row r="191" spans="1:25">
+      <c r="Z190" s="4"/>
+      <c r="AA190" s="4"/>
+    </row>
+    <row r="191" spans="1:27">
       <c r="A191" s="4"/>
       <c r="B191" s="4"/>
       <c r="C191" s="4"/>
@@ -8549,8 +8965,8 @@
       <c r="G191" s="4"/>
       <c r="H191" s="4"/>
       <c r="I191" s="4"/>
-      <c r="Q191" s="4"/>
-      <c r="R191" s="4"/>
+      <c r="J191" s="4"/>
+      <c r="K191" s="4"/>
       <c r="S191" s="4"/>
       <c r="T191" s="4"/>
       <c r="U191" s="4"/>
@@ -8558,8 +8974,10 @@
       <c r="W191" s="4"/>
       <c r="X191" s="4"/>
       <c r="Y191" s="4"/>
-    </row>
-    <row r="192" spans="1:25">
+      <c r="Z191" s="4"/>
+      <c r="AA191" s="4"/>
+    </row>
+    <row r="192" spans="1:27">
       <c r="A192" s="4"/>
       <c r="B192" s="4"/>
       <c r="C192" s="4"/>
@@ -8569,8 +8987,8 @@
       <c r="G192" s="4"/>
       <c r="H192" s="4"/>
       <c r="I192" s="4"/>
-      <c r="Q192" s="4"/>
-      <c r="R192" s="4"/>
+      <c r="J192" s="4"/>
+      <c r="K192" s="4"/>
       <c r="S192" s="4"/>
       <c r="T192" s="4"/>
       <c r="U192" s="4"/>
@@ -8578,8 +8996,10 @@
       <c r="W192" s="4"/>
       <c r="X192" s="4"/>
       <c r="Y192" s="4"/>
-    </row>
-    <row r="193" spans="1:25">
+      <c r="Z192" s="4"/>
+      <c r="AA192" s="4"/>
+    </row>
+    <row r="193" spans="1:27">
       <c r="A193" s="4"/>
       <c r="B193" s="4"/>
       <c r="C193" s="4"/>
@@ -8589,8 +9009,8 @@
       <c r="G193" s="4"/>
       <c r="H193" s="4"/>
       <c r="I193" s="4"/>
-      <c r="Q193" s="4"/>
-      <c r="R193" s="4"/>
+      <c r="J193" s="4"/>
+      <c r="K193" s="4"/>
       <c r="S193" s="4"/>
       <c r="T193" s="4"/>
       <c r="U193" s="4"/>
@@ -8598,6 +9018,8 @@
       <c r="W193" s="4"/>
       <c r="X193" s="4"/>
       <c r="Y193" s="4"/>
+      <c r="Z193" s="4"/>
+      <c r="AA193" s="4"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -8626,13 +9048,13 @@
   <sheetData>
     <row r="1" spans="1:19">
       <c r="A1" s="1" t="s">
-        <v>58</v>
+        <v>62</v>
       </c>
       <c r="B1" s="9" t="s">
-        <v>59</v>
+        <v>63</v>
       </c>
       <c r="C1" s="10" t="s">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="D1" s="10"/>
       <c r="E1" s="10"/>
@@ -8655,31 +9077,31 @@
       <c r="A2" s="1"/>
       <c r="B2" s="9"/>
       <c r="C2" s="11" t="s">
-        <v>61</v>
+        <v>65</v>
       </c>
       <c r="D2" s="11" t="s">
-        <v>62</v>
+        <v>66</v>
       </c>
       <c r="E2" s="11" t="s">
-        <v>63</v>
+        <v>67</v>
       </c>
       <c r="F2" s="11" t="s">
-        <v>64</v>
+        <v>68</v>
       </c>
       <c r="G2" s="11" t="s">
-        <v>65</v>
+        <v>69</v>
       </c>
       <c r="H2" s="11" t="s">
-        <v>66</v>
+        <v>70</v>
       </c>
       <c r="I2" s="11" t="s">
-        <v>67</v>
+        <v>71</v>
       </c>
       <c r="J2" s="11" t="s">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="K2" s="11" t="s">
-        <v>69</v>
+        <v>73</v>
       </c>
       <c r="L2" s="3"/>
       <c r="M2" s="12"/>
@@ -8692,37 +9114,37 @@
     </row>
     <row r="3" spans="1:19">
       <c r="A3" s="4" t="s">
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>71</v>
+        <v>75</v>
       </c>
       <c r="C3" s="4" t="s">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="D3" s="4" t="s">
-        <v>73</v>
+        <v>77</v>
       </c>
       <c r="E3" s="4" t="s">
-        <v>74</v>
+        <v>78</v>
       </c>
       <c r="F3" s="4" t="s">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="G3" s="4" t="s">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="H3" s="4" t="s">
-        <v>77</v>
+        <v>81</v>
       </c>
       <c r="I3" s="4" t="s">
-        <v>78</v>
+        <v>82</v>
       </c>
       <c r="J3" s="4" t="s">
-        <v>79</v>
+        <v>83</v>
       </c>
       <c r="K3" s="4" t="s">
-        <v>80</v>
+        <v>84</v>
       </c>
       <c r="L3" s="3"/>
       <c r="M3" s="3"/>
@@ -11335,16 +11757,16 @@
   <sheetData>
     <row r="1" spans="1:18">
       <c r="A1" s="1" t="s">
-        <v>81</v>
+        <v>85</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>82</v>
+        <v>86</v>
       </c>
       <c r="C1" s="2" t="s">
-        <v>83</v>
+        <v>87</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>84</v>
+        <v>88</v>
       </c>
       <c r="E1" s="1"/>
       <c r="F1" s="1"/>
@@ -11366,31 +11788,31 @@
       <c r="B2" s="2"/>
       <c r="C2" s="2"/>
       <c r="D2" s="7" t="s">
-        <v>61</v>
+        <v>65</v>
       </c>
       <c r="E2" s="7" t="s">
-        <v>62</v>
+        <v>66</v>
       </c>
       <c r="F2" s="7" t="s">
-        <v>63</v>
+        <v>67</v>
       </c>
       <c r="G2" s="7" t="s">
-        <v>64</v>
+        <v>68</v>
       </c>
       <c r="H2" s="7" t="s">
-        <v>65</v>
+        <v>69</v>
       </c>
       <c r="I2" s="7" t="s">
-        <v>66</v>
+        <v>70</v>
       </c>
       <c r="J2" s="7" t="s">
-        <v>67</v>
+        <v>71</v>
       </c>
       <c r="K2" s="7" t="s">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="L2" s="8" t="s">
-        <v>69</v>
+        <v>73</v>
       </c>
       <c r="M2" s="3"/>
       <c r="N2" s="3"/>
@@ -11401,40 +11823,40 @@
     </row>
     <row r="3" spans="1:18">
       <c r="A3" s="4" t="s">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>86</v>
+        <v>90</v>
       </c>
       <c r="C3" s="4" t="s">
-        <v>87</v>
+        <v>91</v>
       </c>
       <c r="D3" s="4" t="s">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="E3" s="4" t="s">
-        <v>73</v>
+        <v>77</v>
       </c>
       <c r="F3" s="4" t="s">
-        <v>74</v>
+        <v>78</v>
       </c>
       <c r="G3" s="4" t="s">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="H3" s="4" t="s">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="I3" s="4" t="s">
-        <v>77</v>
+        <v>81</v>
       </c>
       <c r="J3" s="4" t="s">
-        <v>78</v>
+        <v>82</v>
       </c>
       <c r="K3" s="4" t="s">
-        <v>79</v>
+        <v>83</v>
       </c>
       <c r="L3" s="4" t="s">
-        <v>80</v>
+        <v>84</v>
       </c>
       <c r="M3" s="3"/>
       <c r="N3" s="3"/>
@@ -13855,16 +14277,16 @@
   <sheetData>
     <row r="1" spans="1:18">
       <c r="A1" s="1" t="s">
-        <v>81</v>
+        <v>85</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>82</v>
+        <v>86</v>
       </c>
       <c r="C1" s="2" t="s">
-        <v>83</v>
+        <v>87</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>88</v>
+        <v>92</v>
       </c>
       <c r="E1" s="6"/>
       <c r="F1" s="3"/>
@@ -13883,16 +14305,16 @@
     </row>
     <row r="2" spans="1:17">
       <c r="A2" s="4" t="s">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>86</v>
+        <v>90</v>
       </c>
       <c r="C2" s="4" t="s">
-        <v>87</v>
+        <v>91</v>
       </c>
       <c r="D2" s="4" t="s">
-        <v>71</v>
+        <v>75</v>
       </c>
       <c r="J2" s="4"/>
       <c r="K2" s="4"/>
@@ -16086,22 +16508,22 @@
   <sheetData>
     <row r="1" spans="1:18">
       <c r="A1" s="1" t="s">
-        <v>81</v>
+        <v>85</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>82</v>
+        <v>86</v>
       </c>
       <c r="C1" s="2" t="s">
-        <v>83</v>
+        <v>87</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>89</v>
+        <v>93</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>90</v>
+        <v>94</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>91</v>
+        <v>95</v>
       </c>
       <c r="G1" s="3"/>
       <c r="H1" s="3"/>
@@ -16118,19 +16540,19 @@
     </row>
     <row r="2" spans="1:17">
       <c r="A2" s="4" t="s">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>86</v>
+        <v>90</v>
       </c>
       <c r="C2" s="4" t="s">
-        <v>87</v>
+        <v>91</v>
       </c>
       <c r="D2" s="4" t="s">
         <v>13</v>
       </c>
       <c r="E2" s="4" t="s">
-        <v>92</v>
+        <v>96</v>
       </c>
       <c r="F2" s="4" t="s">
         <v>14</v>

--- a/erp-server/erp-server-file/src/main/resources/excel/mrp/salesCalc.xlsx
+++ b/erp-server/erp-server-file/src/main/resources/excel/mrp/salesCalc.xlsx
@@ -94,7 +94,7 @@
     <t>实际日销量</t>
   </si>
   <si>
-    <t>偏差比例</t>
+    <t>偏差率</t>
   </si>
   <si>
     <t>近 3 日 日均销量</t>
@@ -649,13 +649,13 @@
     </font>
     <font>
       <sz val="9.75"/>
-      <color rgb="FF1F2329"/>
+      <color rgb="FF000000"/>
       <name val="Calibri"/>
       <charset val="134"/>
     </font>
     <font>
       <sz val="9.75"/>
-      <color rgb="FF000000"/>
+      <color rgb="FF1F2329"/>
       <name val="Calibri"/>
       <charset val="134"/>
     </font>
